--- a/characterization/out/out1/out0.xlsx
+++ b/characterization/out/out1/out0.xlsx
@@ -581,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.330537127470952</v>
+        <v>0.3305365349389733</v>
       </c>
       <c r="N2" t="n">
         <v>-0.1502487334696325</v>
@@ -599,1205 +599,1229 @@
         <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
+        <is>
+          <t>Throat Area (mm^2)</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>151.0576068386296</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="C3" t="n">
+        <v>54.611038</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.15920398</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.37653000036088</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7081743279156</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02837827028003411</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.217785702427491e-05</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.217785702427491e-05</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7483222563784864</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="M3" t="n">
+        <v>54.61106029454122</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1592039624843781</v>
+      </c>
+      <c r="O3" t="n">
+        <v>43.98640690669074</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.001266845448831406</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.001266845448831406</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.02946152206584665</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Throat Diameter (mm)</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>13.8684</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.08399999999999999</v>
+      </c>
+      <c r="C4" t="n">
+        <v>329.67749</v>
+      </c>
+      <c r="D4" t="n">
+        <v>73.26915700000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.08399999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.2730471709524</v>
+      </c>
+      <c r="G4" t="n">
+        <v>325.91732955054</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02845614913981376</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0001841840371999084</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0002163618942241833</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.492293590241669</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.08399999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>329.6776245883298</v>
+      </c>
+      <c r="N4" t="n">
+        <v>73.26914893892736</v>
+      </c>
+      <c r="O4" t="n">
+        <v>44.10711938077366</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.007251343962964115</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.00851818941179552</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1768620478771736</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Throat Area (in^2)</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2341397588793937</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="C5" t="n">
+        <v>325.47073</v>
+      </c>
+      <c r="D5" t="n">
+        <v>106.77911</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.2440425703748</v>
+      </c>
+      <c r="G5" t="n">
+        <v>474.9769726842</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02852598958178035</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0001808717744754852</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0003972336686996686</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.41150669452403</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="M5" t="n">
+        <v>325.4708628709519</v>
+      </c>
+      <c r="N5" t="n">
+        <v>106.7790982521623</v>
+      </c>
+      <c r="O5" t="n">
+        <v>44.21537228232725</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.007120939848277301</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01563912926007282</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1736814597140805</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Throat Diameter (in)</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.546</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="C6" t="n">
+        <v>319.22849</v>
+      </c>
+      <c r="D6" t="n">
+        <v>104.72687</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.2010038237124</v>
+      </c>
+      <c r="G6" t="n">
+        <v>465.8481576714</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0285863804936444</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0001722333027206865</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.000569466971420355</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.30583256801716</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="M6" t="n">
+        <v>319.228620322605</v>
+      </c>
+      <c r="N6" t="n">
+        <v>104.7268584779498</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44.30897838292834</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.006780842351443698</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02241997161151652</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1695210587860924</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Burn Time (sec)</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T6" t="n">
         <v>3.159999999999998</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="C3" t="n">
-        <v>54.611038</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.15920398</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.37653000036088</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.7081743279156</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.02837827028003411</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.217785702427491e-05</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.217785702427491e-05</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.7483222563784864</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="M3" t="n">
-        <v>54.61115819234131</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.1592039624843781</v>
-      </c>
-      <c r="O3" t="n">
-        <v>43.98640690669074</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.001266845448831406</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.001266845448831406</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.02946152206584665</v>
-      </c>
-      <c r="S3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="C7" t="n">
+        <v>318.27859</v>
+      </c>
+      <c r="D7" t="n">
+        <v>102.53781</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.1944544911884</v>
+      </c>
+      <c r="G7" t="n">
+        <v>456.1107371982</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02864041428416438</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0001709189495974754</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0007403859210178304</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.272973739936885</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="M7" t="n">
+        <v>318.2787199348155</v>
+      </c>
+      <c r="N7" t="n">
+        <v>102.5377987187901</v>
+      </c>
+      <c r="O7" t="n">
+        <v>44.39273092573906</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.006729096137547567</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02914906774906409</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1682274034386892</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Impulse (N*s)</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T7" t="n">
         <v>1277.394663354039</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.08399999999999999</v>
-      </c>
-      <c r="C4" t="n">
-        <v>329.67749</v>
-      </c>
-      <c r="D4" t="n">
-        <v>73.26915700000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.08399999999999999</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.2730471709524</v>
-      </c>
-      <c r="G4" t="n">
-        <v>325.91732955054</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.02845614913981376</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0001841840371999084</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0002163618942241833</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.492293590241669</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.08399999999999999</v>
-      </c>
-      <c r="M4" t="n">
-        <v>329.6782155805942</v>
-      </c>
-      <c r="N4" t="n">
-        <v>73.26914893892736</v>
-      </c>
-      <c r="O4" t="n">
-        <v>44.10711938077366</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.007251343962964115</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.00851818941179552</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1768620478771736</v>
-      </c>
-      <c r="S4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="C8" t="n">
+        <v>318.68567</v>
+      </c>
+      <c r="D8" t="n">
+        <v>101.68955</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.1972612100892</v>
+      </c>
+      <c r="G8" t="n">
+        <v>452.337490101</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02868954912664206</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001746080679761837</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0009149939889940142</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.258733365272773</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="M8" t="n">
+        <v>318.6858001010028</v>
+      </c>
+      <c r="N8" t="n">
+        <v>101.6895388121157</v>
+      </c>
+      <c r="O8" t="n">
+        <v>44.46889008389748</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.006874337097029152</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03602340484609324</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1676667584641256</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T8" t="n">
         <v>6.84889852893652</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="C5" t="n">
-        <v>325.47073</v>
-      </c>
-      <c r="D5" t="n">
-        <v>106.77911</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.2440425703748</v>
-      </c>
-      <c r="G5" t="n">
-        <v>474.9769726842</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02852598958178035</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0001808717744754852</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0003972336686996686</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.41150669452403</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="M5" t="n">
-        <v>325.4714463220203</v>
-      </c>
-      <c r="N5" t="n">
-        <v>106.7790982521623</v>
-      </c>
-      <c r="O5" t="n">
-        <v>44.21537228232725</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.007120939848277301</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.01563912926007282</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1736814597140805</v>
-      </c>
-      <c r="S5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="C9" t="n">
+        <v>323.97803</v>
+      </c>
+      <c r="D9" t="n">
+        <v>102.13632</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.2337507621228</v>
+      </c>
+      <c r="G9" t="n">
+        <v>454.3248213504</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0287509466447214</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0002580786614133881</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001173072650407402</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.301311023556465</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="M9" t="n">
+        <v>323.9781622615686</v>
+      </c>
+      <c r="N9" t="n">
+        <v>102.1363087629621</v>
+      </c>
+      <c r="O9" t="n">
+        <v>44.56405642725277</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.01016058270771123</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04618398755380447</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1693430451285204</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>C* (m/s)</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T9" t="n">
         <v>1495.643548317361</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="C6" t="n">
-        <v>319.22849</v>
-      </c>
-      <c r="D6" t="n">
-        <v>104.72687</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.2010038237124</v>
-      </c>
-      <c r="G6" t="n">
-        <v>465.8481576714</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0285863804936444</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0001722333027206865</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.000569466971420355</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.30583256801716</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="M6" t="n">
-        <v>319.2291925835991</v>
-      </c>
-      <c r="N6" t="n">
-        <v>104.7268584779498</v>
-      </c>
-      <c r="O6" t="n">
-        <v>44.30897838292834</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.006780842351443698</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.02241997161151652</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1695210587860924</v>
-      </c>
-      <c r="S6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C10" t="n">
+        <v>331.84869</v>
+      </c>
+      <c r="D10" t="n">
+        <v>103.70647</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.2880170738644</v>
+      </c>
+      <c r="G10" t="n">
+        <v>461.3091939834</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02878581654668603</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0001798564406123605</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001352929091019763</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.386742453960013</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="M10" t="n">
+        <v>331.8488254747057</v>
+      </c>
+      <c r="N10" t="n">
+        <v>103.7064585902142</v>
+      </c>
+      <c r="O10" t="n">
+        <v>44.61810488339464</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.007080966052552693</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.05326495360635716</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1727064890866511</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T10" t="n">
         <v>2.167372952195103</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="C7" t="n">
-        <v>318.27859</v>
-      </c>
-      <c r="D7" t="n">
-        <v>102.53781</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.1944544911884</v>
-      </c>
-      <c r="G7" t="n">
-        <v>456.1107371982</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02864041428416438</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0001709189495974754</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0007403859210178304</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.272973739936885</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="M7" t="n">
-        <v>318.2792904929831</v>
-      </c>
-      <c r="N7" t="n">
-        <v>102.5377987187901</v>
-      </c>
-      <c r="O7" t="n">
-        <v>44.39273092573906</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.006729096137547567</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.02914906774906409</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.1682274034386892</v>
-      </c>
-      <c r="S7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="C11" t="n">
+        <v>337.41245</v>
+      </c>
+      <c r="D11" t="n">
+        <v>105.48656</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.326377863762</v>
+      </c>
+      <c r="G11" t="n">
+        <v>469.2274259232</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02881449550009633</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0001821021721907551</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001535031263210518</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.441516394896468</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="M11" t="n">
+        <v>337.4125877460684</v>
+      </c>
+      <c r="N11" t="n">
+        <v>105.4865483943687</v>
+      </c>
+      <c r="O11" t="n">
+        <v>44.66255735008536</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.007169380729367248</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.06043433433572441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1748629446187135</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T11" t="n">
         <v>4.041832530086078</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="C8" t="n">
-        <v>318.68567</v>
-      </c>
-      <c r="D8" t="n">
-        <v>101.68955</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.1972612100892</v>
-      </c>
-      <c r="G8" t="n">
-        <v>452.337490101</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02868954912664206</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0001746080679761837</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0009149939889940142</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.258733365272773</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="M8" t="n">
-        <v>318.6863713889174</v>
-      </c>
-      <c r="N8" t="n">
-        <v>101.6895388121157</v>
-      </c>
-      <c r="O8" t="n">
-        <v>44.46889008389748</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.006874337097029152</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.03602340484609324</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1676667584641256</v>
-      </c>
-      <c r="S8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="C12" t="n">
+        <v>344.33322</v>
+      </c>
+      <c r="D12" t="n">
+        <v>107.12388</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.3740949119272</v>
+      </c>
+      <c r="G12" t="n">
+        <v>476.5105854936</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02883635048721558</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0001805785144917463</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.001715609777702264</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.51446286229366</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="M12" t="n">
+        <v>344.3333605714201</v>
+      </c>
+      <c r="N12" t="n">
+        <v>107.1238682142307</v>
+      </c>
+      <c r="O12" t="n">
+        <v>44.69643264787065</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.007109394173391501</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.06754372850911591</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1777348543347876</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T12" t="n">
         <v>2.763920541652142</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="C9" t="n">
-        <v>323.97803</v>
-      </c>
-      <c r="D9" t="n">
-        <v>102.13632</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.2337507621228</v>
-      </c>
-      <c r="G9" t="n">
-        <v>454.3248213504</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0287509466447214</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0002580786614133881</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001173072650407402</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.301311023556465</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="M9" t="n">
-        <v>323.9787430367667</v>
-      </c>
-      <c r="N9" t="n">
-        <v>102.1363087629621</v>
-      </c>
-      <c r="O9" t="n">
-        <v>44.56405642725277</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.01016058270771123</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.04618398755380447</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.1693430451285204</v>
-      </c>
-      <c r="S9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="C13" t="n">
+        <v>351.79678</v>
+      </c>
+      <c r="D13" t="n">
+        <v>108.75671</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.4255543668728</v>
+      </c>
+      <c r="G13" t="n">
+        <v>483.7737725562</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02885216027161799</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0001883484156748519</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.001903958193377116</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.593863796947609</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="M13" t="n">
+        <v>351.7969236183619</v>
+      </c>
+      <c r="N13" t="n">
+        <v>108.7566980345868</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44.72093786270472</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.007415295959960486</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.0749590244690764</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.180860877072207</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T13" t="n">
         <v>5.111268030844618</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="C10" t="n">
-        <v>331.84869</v>
-      </c>
-      <c r="D10" t="n">
-        <v>103.70647</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.2880170738644</v>
-      </c>
-      <c r="G10" t="n">
-        <v>461.3091939834</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.02878581654668603</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.0001798564406123605</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.001352929091019763</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.386742453960013</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M10" t="n">
-        <v>331.8494203591449</v>
-      </c>
-      <c r="N10" t="n">
-        <v>103.7064585902142</v>
-      </c>
-      <c r="O10" t="n">
-        <v>44.61810488339464</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.007080966052552693</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.05326495360635716</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1727064890866511</v>
-      </c>
-      <c r="S10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C14" t="n">
+        <v>357.63193</v>
+      </c>
+      <c r="D14" t="n">
+        <v>110.6607</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.4657863256868</v>
+      </c>
+      <c r="G14" t="n">
+        <v>492.243138954</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02886090145561306</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.000190731648807937</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.002094689842185053</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.651991434339922</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M14" t="n">
+        <v>357.6320760005175</v>
+      </c>
+      <c r="N14" t="n">
+        <v>110.6606878251098</v>
+      </c>
+      <c r="O14" t="n">
+        <v>44.73448672499476</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.00750912408673336</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.08246814855580975</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1831493679691062</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Impulse (lbf*s)</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T14" t="n">
         <v>287.1698168739581</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C11" t="n">
-        <v>337.41245</v>
-      </c>
-      <c r="D11" t="n">
-        <v>105.48656</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.326377863762</v>
-      </c>
-      <c r="G11" t="n">
-        <v>469.2274259232</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.02881449550009633</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.0001821021721907551</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.001535031263210518</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.441516394896468</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="M11" t="n">
-        <v>337.413192604313</v>
-      </c>
-      <c r="N11" t="n">
-        <v>105.4865483943687</v>
-      </c>
-      <c r="O11" t="n">
-        <v>44.66255735008536</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.007169380729367248</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.06043433433572441</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1748629446187135</v>
-      </c>
-      <c r="S11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="C15" t="n">
+        <v>364.8241</v>
+      </c>
+      <c r="D15" t="n">
+        <v>111.70895</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.515374611716</v>
+      </c>
+      <c r="G15" t="n">
+        <v>496.905985569</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.02886229099668536</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0001938383819785616</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.002288528224163614</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.727765414111254</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="M15" t="n">
+        <v>364.8242489366662</v>
+      </c>
+      <c r="N15" t="n">
+        <v>111.7089377097813</v>
+      </c>
+      <c r="O15" t="n">
+        <v>44.73664051796439</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.007631436482334168</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09009958503814391</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1861325971301015</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T15" t="n">
         <v>993.3487485792778</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="C12" t="n">
-        <v>344.33322</v>
-      </c>
-      <c r="D12" t="n">
-        <v>107.12388</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.3740949119272</v>
-      </c>
-      <c r="G12" t="n">
-        <v>476.5105854936</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.02883635048721558</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0001805785144917463</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.001715609777702264</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.51446286229366</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.428</v>
-      </c>
-      <c r="M12" t="n">
-        <v>344.3339778360972</v>
-      </c>
-      <c r="N12" t="n">
-        <v>107.1238682142307</v>
-      </c>
-      <c r="O12" t="n">
-        <v>44.69643264787065</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.007109394173391501</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.06754372850911591</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1777348543347876</v>
-      </c>
-      <c r="S12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.5920000000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>366.85962</v>
+      </c>
+      <c r="D16" t="n">
+        <v>113.47612</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5920000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5294090335912</v>
+      </c>
+      <c r="G16" t="n">
+        <v>504.7667465064</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.02885610616486634</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0001942242927042373</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.002482752516867852</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.737177870835051</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5920000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>366.8597697676518</v>
+      </c>
+      <c r="N16" t="n">
+        <v>113.4761075153573</v>
+      </c>
+      <c r="O16" t="n">
+        <v>44.72705400947194</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.007646629826195092</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.09774621486433901</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.186503166492563</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>C* (ft/s)</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>4906.967022018958</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="C13" t="n">
-        <v>351.79678</v>
-      </c>
-      <c r="D13" t="n">
-        <v>108.75671</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.4255543668728</v>
-      </c>
-      <c r="G13" t="n">
-        <v>483.7737725562</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.02885216027161799</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0001883484156748519</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.001903958193377116</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.593863796947609</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="M13" t="n">
-        <v>351.7975542624972</v>
-      </c>
-      <c r="N13" t="n">
-        <v>108.7566980345868</v>
-      </c>
-      <c r="O13" t="n">
-        <v>44.72093786270472</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.007415295959960486</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.0749590244690764</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.180860877072207</v>
-      </c>
-      <c r="S13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6330000000000001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>371.47345</v>
+      </c>
+      <c r="D17" t="n">
+        <v>113.74528</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6330000000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.561220284122</v>
+      </c>
+      <c r="G17" t="n">
+        <v>505.9640294016</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02884217620144304</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0001959953729437659</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.002678747889811618</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.780374949847944</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6330000000000001</v>
+      </c>
+      <c r="M17" t="n">
+        <v>371.4736016512128</v>
+      </c>
+      <c r="N17" t="n">
+        <v>113.7452674857443</v>
+      </c>
+      <c r="O17" t="n">
+        <v>44.70546252298293</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.007716357432333358</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1054625722966724</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1882038398130086</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>314.3508698035691</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="C14" t="n">
-        <v>357.63193</v>
-      </c>
-      <c r="D14" t="n">
-        <v>110.6607</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.4657863256868</v>
-      </c>
-      <c r="G14" t="n">
-        <v>492.243138954</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.02886090145561306</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.000190731648807937</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.002094689842185053</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.651991434339922</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="M14" t="n">
-        <v>357.6327171049621</v>
-      </c>
-      <c r="N14" t="n">
-        <v>110.6606878251098</v>
-      </c>
-      <c r="O14" t="n">
-        <v>44.73448672499476</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.00750912408673336</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.08246814855580975</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.1831493679691062</v>
-      </c>
-      <c r="S14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6760000000000002</v>
+      </c>
+      <c r="C18" t="n">
+        <v>375.54446</v>
+      </c>
+      <c r="D18" t="n">
+        <v>114.72587</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6760000000000002</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.5892889210296</v>
+      </c>
+      <c r="G18" t="n">
+        <v>510.3259094514</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.02881906445312333</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0002071008756080983</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.002885848765419716</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.816299432746468</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6760000000000002</v>
+      </c>
+      <c r="M18" t="n">
+        <v>375.5446133131717</v>
+      </c>
+      <c r="N18" t="n">
+        <v>114.7258573778598</v>
+      </c>
+      <c r="O18" t="n">
+        <v>44.66963924144095</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.008153582182778391</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1136161544794508</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1896181902971717</v>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Average Burnrate (in/s) (using full fire)</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>0.1591273508927419</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="C15" t="n">
-        <v>364.8241</v>
-      </c>
-      <c r="D15" t="n">
-        <v>111.70895</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.515374611716</v>
-      </c>
-      <c r="G15" t="n">
-        <v>496.905985569</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.02886229099668536</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0001938383819785616</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.002288528224163614</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.727765414111254</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.551</v>
-      </c>
-      <c r="M15" t="n">
-        <v>364.8249029340652</v>
-      </c>
-      <c r="N15" t="n">
-        <v>111.7089377097813</v>
-      </c>
-      <c r="O15" t="n">
-        <v>44.73664051796439</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.007631436482334168</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.09009958503814391</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.1861325971301015</v>
-      </c>
-      <c r="S15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7350000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>380.15836</v>
+      </c>
+      <c r="D19" t="n">
+        <v>115.42886</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7350000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.6211006541936</v>
+      </c>
+      <c r="G19" t="n">
+        <v>513.4529636292</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02877289515893049</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0002863953909447703</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.003172244156364486</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.854159168555433</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7350000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>380.1585151967614</v>
+      </c>
+      <c r="N19" t="n">
+        <v>115.4288473005168</v>
+      </c>
+      <c r="O19" t="n">
+        <v>44.59807669231724</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0112754151810347</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1248915696604855</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1911087318819442</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (psig)</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T19" t="n">
         <v>400.8727826267029</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5920000000000001</v>
-      </c>
-      <c r="C16" t="n">
-        <v>366.85962</v>
-      </c>
-      <c r="D16" t="n">
-        <v>113.47612</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.5920000000000001</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.5294090335912</v>
-      </c>
-      <c r="G16" t="n">
-        <v>504.7667465064</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.02885610616486634</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0001942242927042373</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.002482752516867852</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.737177870835051</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.5920000000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>366.8604274140005</v>
-      </c>
-      <c r="N16" t="n">
-        <v>113.4761075153573</v>
-      </c>
-      <c r="O16" t="n">
-        <v>44.72705400947194</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.007646629826195092</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.09774621486433901</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.186503166492563</v>
-      </c>
-      <c r="S16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7760000000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>385.5864</v>
+      </c>
+      <c r="D20" t="n">
+        <v>115.75622</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7760000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.658525687264</v>
+      </c>
+      <c r="G20" t="n">
+        <v>514.9091329284</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02873057718340393</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0002012883892764383</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.003373532545640924</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.909472909181418</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7760000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>385.5865574127174</v>
+      </c>
+      <c r="N20" t="n">
+        <v>115.7562072645007</v>
+      </c>
+      <c r="O20" t="n">
+        <v>44.53248369906537</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.007924744014652305</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1328163136751377</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1932864393817633</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (in/s)</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T20" t="n">
         <v>0.2012311335011557</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.6330000000000001</v>
-      </c>
-      <c r="C17" t="n">
-        <v>371.47345</v>
-      </c>
-      <c r="D17" t="n">
-        <v>113.74528</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6330000000000001</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.561220284122</v>
-      </c>
-      <c r="G17" t="n">
-        <v>505.9640294016</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.02884217620144304</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0001959953729437659</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.002678747889811618</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.780374949847944</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.6330000000000001</v>
-      </c>
-      <c r="M17" t="n">
-        <v>371.4742675684867</v>
-      </c>
-      <c r="N17" t="n">
-        <v>113.7452674857443</v>
-      </c>
-      <c r="O17" t="n">
-        <v>44.70546252298293</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.007716357432333358</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.1054625722966724</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.1882038398130086</v>
-      </c>
-      <c r="S17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.8170000000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>389.92883</v>
+      </c>
+      <c r="D21" t="n">
+        <v>116.45522</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8170000000000002</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.6884656999308</v>
+      </c>
+      <c r="G21" t="n">
+        <v>518.0184387084</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02867964581589636</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0002030107622758009</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.003576543307916725</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.951482006726848</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8170000000000002</v>
+      </c>
+      <c r="M21" t="n">
+        <v>389.9289891854815</v>
+      </c>
+      <c r="N21" t="n">
+        <v>116.4552071875967</v>
+      </c>
+      <c r="O21" t="n">
+        <v>44.45353992154138</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.007992554011874511</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1408088676870123</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1949403417530367</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>ISP (sec)</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T21" t="n">
         <v>188.2438775450109</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.6760000000000002</v>
-      </c>
-      <c r="C18" t="n">
-        <v>375.54446</v>
-      </c>
-      <c r="D18" t="n">
-        <v>114.72587</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.6760000000000002</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.5892889210296</v>
-      </c>
-      <c r="G18" t="n">
-        <v>510.3259094514</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02881906445312333</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.0002071008756080983</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.002885848765419716</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.816299432746468</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6760000000000002</v>
-      </c>
-      <c r="M18" t="n">
-        <v>375.5452865282912</v>
-      </c>
-      <c r="N18" t="n">
-        <v>114.7258573778598</v>
-      </c>
-      <c r="O18" t="n">
-        <v>44.66963924144095</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.008153582182778391</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1136161544794508</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.1896181902971717</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.7350000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>380.15836</v>
-      </c>
-      <c r="D19" t="n">
-        <v>115.42886</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7350000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.6211006541936</v>
-      </c>
-      <c r="G19" t="n">
-        <v>513.4529636292</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.02877289515893049</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.0002863953909447703</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.003172244156364486</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.854159168555433</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7350000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>380.1591966829314</v>
-      </c>
-      <c r="N19" t="n">
-        <v>115.4288473005168</v>
-      </c>
-      <c r="O19" t="n">
-        <v>44.59807669231724</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.0112754151810347</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1248915696604855</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.1911087318819442</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.7760000000000001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>385.5864</v>
-      </c>
-      <c r="D20" t="n">
-        <v>115.75622</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.7760000000000001</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.658525687264</v>
-      </c>
-      <c r="G20" t="n">
-        <v>514.9091329284</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.02873057718340393</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0002012883892764383</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.003373532545640924</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.909472909181418</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7760000000000001</v>
-      </c>
-      <c r="M20" t="n">
-        <v>385.5872486293961</v>
-      </c>
-      <c r="N20" t="n">
-        <v>115.7562072645007</v>
-      </c>
-      <c r="O20" t="n">
-        <v>44.53248369906537</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.007924744014652305</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1328163136751377</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.1932864393817633</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.8170000000000002</v>
-      </c>
-      <c r="C21" t="n">
-        <v>389.92883</v>
-      </c>
-      <c r="D21" t="n">
-        <v>116.45522</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8170000000000002</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.6884656999308</v>
-      </c>
-      <c r="G21" t="n">
-        <v>518.0184387084</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02867964581589636</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.0002030107622758009</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.003576543307916725</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.951482006726848</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.8170000000000002</v>
-      </c>
-      <c r="M21" t="n">
-        <v>389.9296881865634</v>
-      </c>
-      <c r="N21" t="n">
-        <v>116.4552071875967</v>
-      </c>
-      <c r="O21" t="n">
-        <v>44.45353992154138</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.007992554011874511</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.1408088676870123</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.1949403417530367</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1837,7 +1861,7 @@
         <v>0.8570000000000002</v>
       </c>
       <c r="M22" t="n">
-        <v>395.3577401330281</v>
+        <v>395.3570314014375</v>
       </c>
       <c r="N22" t="n">
         <v>117.099487116713</v>
@@ -1895,7 +1919,7 @@
         <v>0.8980000000000002</v>
       </c>
       <c r="M23" t="n">
-        <v>400.7857920794928</v>
+        <v>400.7850736173936</v>
       </c>
       <c r="N23" t="n">
         <v>117.5935170623598</v>
@@ -1953,7 +1977,7 @@
         <v>0.9410000000000003</v>
       </c>
       <c r="M24" t="n">
-        <v>404.449740143385</v>
+        <v>404.4490151131693</v>
       </c>
       <c r="N24" t="n">
         <v>118.7542169346596</v>
@@ -2011,7 +2035,7 @@
         <v>0.9820000000000003</v>
       </c>
       <c r="M25" t="n">
-        <v>408.6565094019589</v>
+        <v>408.655776830547</v>
       </c>
       <c r="N25" t="n">
         <v>119.1452568916374</v>
@@ -2069,7 +2093,7 @@
         <v>1.022</v>
       </c>
       <c r="M26" t="n">
-        <v>412.0490368684884</v>
+        <v>412.0482982155176</v>
       </c>
       <c r="N26" t="n">
         <v>119.5472468474105</v>
@@ -2127,7 +2151,7 @@
         <v>1.063</v>
       </c>
       <c r="M27" t="n">
-        <v>414.7630628417207</v>
+        <v>414.7623193234957</v>
       </c>
       <c r="N27" t="n">
         <v>120.1855567771836</v>
@@ -2185,7 +2209,7 @@
         <v>1.104</v>
       </c>
       <c r="M28" t="n">
-        <v>420.1911147881854</v>
+        <v>420.1903615394516</v>
       </c>
       <c r="N28" t="n">
         <v>120.2079467747202</v>
@@ -2243,7 +2267,7 @@
         <v>1.163</v>
       </c>
       <c r="M29" t="n">
-        <v>426.0262676306284</v>
+        <v>426.0255039216033</v>
       </c>
       <c r="N29" t="n">
         <v>121.4850666342115</v>
@@ -2301,7 +2325,7 @@
         <v>1.204</v>
       </c>
       <c r="M30" t="n">
-        <v>428.3332227079485</v>
+        <v>428.3324548633981</v>
       </c>
       <c r="N30" t="n">
         <v>122.1855565571436</v>
@@ -2359,7 +2383,7 @@
         <v>1.245</v>
       </c>
       <c r="M31" t="n">
-        <v>429.9616062918174</v>
+        <v>429.9608355281719</v>
       </c>
       <c r="N31" t="n">
         <v>122.3855565351396</v>
@@ -2417,7 +2441,7 @@
         <v>1.285</v>
       </c>
       <c r="M32" t="n">
-        <v>434.1683755503913</v>
+        <v>434.1675972455496</v>
       </c>
       <c r="N32" t="n">
         <v>122.2547065495357</v>
@@ -2475,7 +2499,7 @@
         <v>1.329</v>
       </c>
       <c r="M33" t="n">
-        <v>435.5253985370296</v>
+        <v>435.5246177995427</v>
       </c>
       <c r="N33" t="n">
         <v>123.0109364663353</v>
@@ -2533,7 +2557,7 @@
         <v>1.37</v>
       </c>
       <c r="M34" t="n">
-        <v>437.4252227183054</v>
+        <v>437.4244385751298</v>
       </c>
       <c r="N34" t="n">
         <v>122.9741164703862</v>
@@ -2591,7 +2615,7 @@
         <v>1.411</v>
       </c>
       <c r="M35" t="n">
-        <v>440.9534504834942</v>
+        <v>440.9526600154987</v>
       </c>
       <c r="N35" t="n">
         <v>123.0845664582345</v>
@@ -2649,7 +2673,7 @@
         <v>1.451</v>
       </c>
       <c r="M36" t="n">
-        <v>443.80319675543</v>
+        <v>443.8024011788834</v>
       </c>
       <c r="N36" t="n">
         <v>123.466156416252</v>
@@ -2707,7 +2731,7 @@
         <v>1.492</v>
       </c>
       <c r="M37" t="n">
-        <v>446.2457921312774</v>
+        <v>446.2449921760523</v>
       </c>
       <c r="N37" t="n">
         <v>123.9213763661687</v>
@@ -2765,7 +2789,7 @@
         <v>1.533</v>
       </c>
       <c r="M38" t="n">
-        <v>448.688427507213</v>
+        <v>448.6876231732374</v>
       </c>
       <c r="N38" t="n">
         <v>124.099986346518</v>
@@ -2823,7 +2847,7 @@
         <v>1.592</v>
       </c>
       <c r="M39" t="n">
-        <v>450.7239519871482</v>
+        <v>450.7231440042229</v>
       </c>
       <c r="N39" t="n">
         <v>124.1298363432339</v>
@@ -2881,7 +2905,7 @@
         <v>1.633</v>
       </c>
       <c r="M40" t="n">
-        <v>452.0810149738745</v>
+        <v>452.0802045582324</v>
       </c>
       <c r="N40" t="n">
         <v>123.931826365019</v>
@@ -2939,7 +2963,7 @@
         <v>1.673999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>453.9808291551283</v>
+        <v>453.9800153338154</v>
       </c>
       <c r="N41" t="n">
         <v>123.8472563743234</v>
@@ -2997,7 +3021,7 @@
         <v>1.714999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>456.2877442323604</v>
+        <v>456.2869262755939</v>
       </c>
       <c r="N42" t="n">
         <v>123.831326376076</v>
@@ -3055,7 +3079,7 @@
         <v>1.754999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>457.5090669203391</v>
+        <v>457.5082467741885</v>
       </c>
       <c r="N43" t="n">
         <v>123.897496368796</v>
@@ -3113,7 +3137,7 @@
         <v>1.795999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>460.087372594868</v>
+        <v>460.0865478267599</v>
       </c>
       <c r="N44" t="n">
         <v>123.896496368906</v>
@@ -3171,7 +3195,7 @@
         <v>1.836999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>460.3587731921868</v>
+        <v>460.3579479375568</v>
       </c>
       <c r="N45" t="n">
         <v>123.968146361023</v>
@@ -3229,7 +3253,7 @@
         <v>1.877999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>463.6156103600788</v>
+        <v>463.6147792671329</v>
       </c>
       <c r="N46" t="n">
         <v>123.9711363606941</v>
@@ -3287,7 +3311,7 @@
         <v>1.918999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>461.5800858801437</v>
+        <v>461.5792584361474</v>
       </c>
       <c r="N47" t="n">
         <v>124.400486313457</v>
@@ -3345,7 +3369,7 @@
         <v>1.961999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>442.9890149635175</v>
+        <v>442.9882208465007</v>
       </c>
       <c r="N48" t="n">
         <v>123.8875563698896</v>
@@ -3403,7 +3427,7 @@
         <v>2.020999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>372.4241896591466</v>
+        <v>372.4235220390104</v>
       </c>
       <c r="N49" t="n">
         <v>115.9437672438653</v>
@@ -3461,7 +3485,7 @@
         <v>2.062999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>322.7574203487879</v>
+        <v>322.756841762974</v>
       </c>
       <c r="N50" t="n">
         <v>101.0497388825065</v>
@@ -3519,7 +3543,7 @@
         <v>2.103999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>302.1307949521606</v>
+        <v>302.1302533423294</v>
       </c>
       <c r="N51" t="n">
         <v>86.52138348091636</v>
@@ -3577,7 +3601,7 @@
         <v>2.144999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>294.802898824376</v>
+        <v>294.8023703507781</v>
       </c>
       <c r="N52" t="n">
         <v>81.85919799385005</v>
@@ -3635,7 +3659,7 @@
         <v>2.185999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>291.1389807605498</v>
+        <v>291.1384588550147</v>
       </c>
       <c r="N53" t="n">
         <v>79.60496424186087</v>
@@ -3693,7 +3717,7 @@
         <v>2.225999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>288.9677359819111</v>
+        <v>288.9672179686225</v>
       </c>
       <c r="N54" t="n">
         <v>78.81193432911004</v>
@@ -3751,7 +3775,7 @@
         <v>2.266999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>286.660820904679</v>
+        <v>286.660307026844</v>
       </c>
       <c r="N55" t="n">
         <v>77.98506842008183</v>
@@ -3809,7 +3833,7 @@
         <v>2.307999999999998</v>
       </c>
       <c r="M56" t="n">
-        <v>283.5396840354464</v>
+        <v>283.5391757526664</v>
       </c>
       <c r="N56" t="n">
         <v>77.4099414833573</v>
@@ -3867,7 +3891,7 @@
         <v>2.347999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>280.5542374648512</v>
+        <v>280.5537345338832</v>
       </c>
       <c r="N57" t="n">
         <v>76.39601059491</v>
@@ -3925,7 +3949,7 @@
         <v>2.388999999999998</v>
       </c>
       <c r="M58" t="n">
-        <v>280.4185571662358</v>
+        <v>280.4180544784928</v>
       </c>
       <c r="N58" t="n">
         <v>75.81043965933451</v>
@@ -3983,7 +4007,7 @@
         <v>2.447999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>277.0260296997064</v>
+        <v>277.0255330935224</v>
       </c>
       <c r="N59" t="n">
         <v>75.48606069502269</v>
@@ -4041,7 +4065,7 @@
         <v>2.488999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>275.2618958170679</v>
+        <v>275.2614023733296</v>
       </c>
       <c r="N60" t="n">
         <v>74.90447175900913</v>
@@ -4099,7 +4123,7 @@
         <v>2.528999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>267.2554981959863</v>
+        <v>267.2550191047859</v>
       </c>
       <c r="N61" t="n">
         <v>74.34576382047817</v>
@@ -4157,7 +4181,7 @@
         <v>2.569999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>247.7144851886563</v>
+        <v>247.7140411273334</v>
       </c>
       <c r="N62" t="n">
         <v>72.04128207401727</v>
@@ -4215,7 +4239,7 @@
         <v>2.610999999999998</v>
       </c>
       <c r="M63" t="n">
-        <v>218.8100415735844</v>
+        <v>218.8096493273399</v>
       </c>
       <c r="N63" t="n">
         <v>67.42884858147725</v>
@@ -4273,7 +4297,7 @@
         <v>2.653999999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>185.4274581026858</v>
+        <v>185.4271256991839</v>
       </c>
       <c r="N64" t="n">
         <v>57.99451961944225</v>
@@ -4331,7 +4355,7 @@
         <v>2.694999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>152.1805749304466</v>
+        <v>152.1803021264264</v>
       </c>
       <c r="N65" t="n">
         <v>47.73531974815955</v>
@@ -4389,7 +4413,7 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>122.3262392247809</v>
+        <v>122.3260199386476</v>
       </c>
       <c r="N66" t="n">
         <v>39.56168664742276</v>
@@ -4447,7 +4471,7 @@
         <v>2.775999999999998</v>
       </c>
       <c r="M67" t="n">
-        <v>99.6640763481896</v>
+        <v>99.66389768701218</v>
       </c>
       <c r="N67" t="n">
         <v>29.7731307243598</v>
@@ -4505,7 +4529,7 @@
         <v>2.816999999999998</v>
       </c>
       <c r="M68" t="n">
-        <v>71.70955382377547</v>
+        <v>71.70942527481593</v>
       </c>
       <c r="N68" t="n">
         <v>23.86815537402526</v>
@@ -4563,7 +4587,7 @@
         <v>2.874999999999998</v>
       </c>
       <c r="M69" t="n">
-        <v>47.82607925922966</v>
+        <v>47.82599352459041</v>
       </c>
       <c r="N69" t="n">
         <v>15.39601830612988</v>
@@ -4621,7 +4645,7 @@
         <v>2.915999999999998</v>
       </c>
       <c r="M70" t="n">
-        <v>36.56285147027144</v>
+        <v>36.56278592647339</v>
       </c>
       <c r="N70" t="n">
         <v>11.31094475556972</v>
@@ -4679,7 +4703,7 @@
         <v>2.955999999999998</v>
       </c>
       <c r="M71" t="n">
-        <v>29.64207123849816</v>
+        <v>29.64201810112367</v>
       </c>
       <c r="N71" t="n">
         <v>9.198506287980226</v>
@@ -4737,7 +4761,7 @@
         <v>2.996999999999998</v>
       </c>
       <c r="M72" t="n">
-        <v>21.77138391609798</v>
+        <v>21.77134488798246</v>
       </c>
       <c r="N72" t="n">
         <v>6.954725434841023</v>
@@ -4795,7 +4819,7 @@
         <v>3.037999999999998</v>
       </c>
       <c r="M73" t="n">
-        <v>2.366060207403128</v>
+        <v>2.366055965923972</v>
       </c>
       <c r="N73" t="n">
         <v>5.260198521272896</v>
@@ -4853,7 +4877,7 @@
         <v>3.078999999999998</v>
       </c>
       <c r="M74" t="n">
-        <v>0.8733433621197085</v>
+        <v>0.8733417965350057</v>
       </c>
       <c r="N74" t="n">
         <v>4.412437414543581</v>
@@ -4911,7 +4935,7 @@
         <v>3.118999999999998</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.2122691071778044</v>
+        <v>-0.2122687266570591</v>
       </c>
       <c r="N75" t="n">
         <v>4.04626805482954</v>
@@ -4969,7 +4993,7 @@
         <v>3.159999999999998</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.8907770404890581</v>
+        <v>-0.8907754436521567</v>
       </c>
       <c r="N76" t="n">
         <v>3.53532301104372</v>
@@ -5138,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.134844197650401</v>
+        <v>1.134842163290499</v>
       </c>
       <c r="N2" t="n">
         <v>-1.277611859437128</v>
@@ -5156,1205 +5180,1229 @@
         <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
+        <is>
+          <t>Throat Area (mm^2)</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>142.8717475138095</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="C3" t="n">
+        <v>292.48544</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.60049748</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.0166169122944</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.6711449004856</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02842843366025913</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0001489429337362628</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0001489429337362628</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.632754481372264</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="M3" t="n">
+        <v>292.485559404958</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.6004974139332674</v>
+      </c>
+      <c r="O3" t="n">
+        <v>44.064160301546</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.005863898195490042</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.005863898195490042</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1430219072070742</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Throat Diameter (mm)</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>13.4874</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>335.63843</v>
+      </c>
+      <c r="D4" t="n">
+        <v>84.974129</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.3141464216268</v>
+      </c>
+      <c r="G4" t="n">
+        <v>377.9836201003801</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02852447814317138</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0002441875968425504</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0003931305305788132</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.138772827839836</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>335.6385670218382</v>
+      </c>
+      <c r="N4" t="n">
+        <v>84.97411965114634</v>
+      </c>
+      <c r="O4" t="n">
+        <v>44.21302954779788</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.009613690106450893</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01547758830194093</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1629439001093372</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Throat Area (in^2)</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2214516515497079</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="C5" t="n">
+        <v>337.12256</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99.594528</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.3243791417856</v>
+      </c>
+      <c r="G5" t="n">
+        <v>443.01837134016</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02858413788104548</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0001696219230070871</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0005627524535859003</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.137120073343586</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="M5" t="n">
+        <v>337.122697627723</v>
+      </c>
+      <c r="N5" t="n">
+        <v>99.59451704261004</v>
+      </c>
+      <c r="O5" t="n">
+        <v>44.30550232644793</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.006678032070981318</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02215562037292225</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1628788309995443</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Throat Diameter (in)</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.531</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="C6" t="n">
+        <v>334.2814</v>
+      </c>
+      <c r="D6" t="n">
+        <v>99.037811</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.304790025464</v>
+      </c>
+      <c r="G6" t="n">
+        <v>440.5419716464201</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.02863735096513131</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0001674217527505562</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0007301742063364565</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.083457384159908</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="M6" t="n">
+        <v>334.2815364678411</v>
+      </c>
+      <c r="N6" t="n">
+        <v>99.03780010386005</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44.38798277174153</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.006591411147964674</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02874703152088693</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.160766125560114</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Burn Time (sec)</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T6" t="n">
         <v>3.001999999999998</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="C3" t="n">
-        <v>292.48544</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-0.60049748</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2.0166169122944</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-2.6711449004856</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.02842843366025913</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0001489429337362628</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0001489429337362628</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.632754481372264</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="M3" t="n">
-        <v>292.4860837253552</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-0.6004974139332674</v>
-      </c>
-      <c r="O3" t="n">
-        <v>44.064160301546</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.005863898195490042</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.005863898195490042</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1430219072070742</v>
-      </c>
-      <c r="S3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="C7" t="n">
+        <v>335.36703</v>
+      </c>
+      <c r="D7" t="n">
+        <v>98.04129</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.3122751837628</v>
+      </c>
+      <c r="G7" t="n">
+        <v>436.1092270038</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02868378738032369</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0001631610859640342</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0008933352923004907</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.079027149100853</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="M7" t="n">
+        <v>335.3671669110412</v>
+      </c>
+      <c r="N7" t="n">
+        <v>98.04127921349728</v>
+      </c>
+      <c r="O7" t="n">
+        <v>44.4599593592426</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.006423668270512621</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.03517069979139955</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1605917067628155</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Impulse (N*s)</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T7" t="n">
         <v>1246.81150462104</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>335.63843</v>
-      </c>
-      <c r="D4" t="n">
-        <v>84.974129</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.3141464216268</v>
-      </c>
-      <c r="G4" t="n">
-        <v>377.9836201003801</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.02852447814317138</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0002441875968425504</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0003931305305788132</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.138772827839836</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>335.6391686999078</v>
-      </c>
-      <c r="N4" t="n">
-        <v>84.97411965114634</v>
-      </c>
-      <c r="O4" t="n">
-        <v>44.21302954779788</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.009613690106450893</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.01547758830194093</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1629439001093372</v>
-      </c>
-      <c r="S4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="C8" t="n">
+        <v>338.08105</v>
+      </c>
+      <c r="D8" t="n">
+        <v>98.31144</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.330987700298</v>
+      </c>
+      <c r="G8" t="n">
+        <v>437.3109136368</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02872882914801152</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001800974771407315</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.001073432769441222</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.093124480471172</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="M8" t="n">
+        <v>338.0811880190193</v>
+      </c>
+      <c r="N8" t="n">
+        <v>98.31142918377537</v>
+      </c>
+      <c r="O8" t="n">
+        <v>44.52977423878821</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.007090455684778313</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.04226115547617786</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1611467201085981</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T8" t="n">
         <v>7.529171700599465</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="C5" t="n">
-        <v>337.12256</v>
-      </c>
-      <c r="D5" t="n">
-        <v>99.594528</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.3243791417856</v>
-      </c>
-      <c r="G5" t="n">
-        <v>443.01837134016</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02858413788104548</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0001696219230070871</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.0005627524535859003</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.137120073343586</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="M5" t="n">
-        <v>337.1233019662999</v>
-      </c>
-      <c r="N5" t="n">
-        <v>99.59451704261004</v>
-      </c>
-      <c r="O5" t="n">
-        <v>44.30550232644793</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.006678032070981318</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.02215562037292225</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1628788309995443</v>
-      </c>
-      <c r="S5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="C9" t="n">
+        <v>340.65939</v>
+      </c>
+      <c r="D9" t="n">
+        <v>99.188057</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.3487647357964</v>
+      </c>
+      <c r="G9" t="n">
+        <v>441.21029890854</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.02876423272774328</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001643060434849185</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001237738812926141</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.107651087122964</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="M9" t="n">
+        <v>340.659529071607</v>
+      </c>
+      <c r="N9" t="n">
+        <v>99.18804608732997</v>
+      </c>
+      <c r="O9" t="n">
+        <v>44.58464989712353</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.006468745362605588</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04872990083878345</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1617186340651398</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>C* (m/s)</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T9" t="n">
         <v>1555.10002373212</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="C6" t="n">
-        <v>334.2814</v>
-      </c>
-      <c r="D6" t="n">
-        <v>99.037811</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.304790025464</v>
-      </c>
-      <c r="G6" t="n">
-        <v>440.5419716464201</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02863735096513131</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0001674217527505562</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.0007301742063364565</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.083457384159908</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="M6" t="n">
-        <v>334.2821357132477</v>
-      </c>
-      <c r="N6" t="n">
-        <v>99.03780010386005</v>
-      </c>
-      <c r="O6" t="n">
-        <v>44.38798277174153</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.006591411147964674</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.02874703152088693</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.160766125560114</v>
-      </c>
-      <c r="S6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C10" t="n">
+        <v>342.96631</v>
+      </c>
+      <c r="D10" t="n">
+        <v>99.800995</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.364670395535601</v>
+      </c>
+      <c r="G10" t="n">
+        <v>443.9367819789</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02879496417759991</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0001688741012494819</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001406612914175623</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.118880518280048</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="M10" t="n">
+        <v>342.9664500133896</v>
+      </c>
+      <c r="N10" t="n">
+        <v>99.80098401989453</v>
+      </c>
+      <c r="O10" t="n">
+        <v>44.63228373966881</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.006648590253602227</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.05537849109238568</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1621607378927373</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T10" t="n">
         <v>2.508051865622741</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="C7" t="n">
-        <v>335.36703</v>
-      </c>
-      <c r="D7" t="n">
-        <v>98.04129</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.3122751837628</v>
-      </c>
-      <c r="G7" t="n">
-        <v>436.1092270038</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02868378738032369</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0001631610859640342</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0008933352923004907</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.079027149100853</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="M7" t="n">
-        <v>335.367768102589</v>
-      </c>
-      <c r="N7" t="n">
-        <v>98.04127921349728</v>
-      </c>
-      <c r="O7" t="n">
-        <v>44.4599593592426</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.006423668270512621</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.03517069979139955</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.1605917067628155</v>
-      </c>
-      <c r="S7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="C11" t="n">
+        <v>346.76593</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100.67264</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.3908678635268</v>
+      </c>
+      <c r="G11" t="n">
+        <v>447.8140507008</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02882011964259153</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.000170080830607604</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001576693744783227</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.14831294164888</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="M11" t="n">
+        <v>346.7660715645556</v>
+      </c>
+      <c r="N11" t="n">
+        <v>100.6726289239962</v>
+      </c>
+      <c r="O11" t="n">
+        <v>44.67127478838777</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.006696099309104432</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.06207459040149011</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1633194953440106</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T11" t="n">
         <v>4.254978472732983</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="C8" t="n">
-        <v>338.08105</v>
-      </c>
-      <c r="D8" t="n">
-        <v>98.31144</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.330987700298</v>
-      </c>
-      <c r="G8" t="n">
-        <v>437.3109136368</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02872882914801152</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0001800974771407315</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.001073432769441222</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.093124480471172</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="M8" t="n">
-        <v>338.0817940758213</v>
-      </c>
-      <c r="N8" t="n">
-        <v>98.31142918377537</v>
-      </c>
-      <c r="O8" t="n">
-        <v>44.52977423878821</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.007090455684778313</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.04226115547617786</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1611467201085981</v>
-      </c>
-      <c r="S8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4289999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>351.37979</v>
+      </c>
+      <c r="D12" t="n">
+        <v>101.42487</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4289999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.4226793209004</v>
+      </c>
+      <c r="G12" t="n">
+        <v>451.1601352314</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.0288396143833411</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0001716930582947985</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.001748386803078025</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.187635568165818</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4289999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>351.3799334481288</v>
+      </c>
+      <c r="N12" t="n">
+        <v>101.4248588412358</v>
+      </c>
+      <c r="O12" t="n">
+        <v>44.70149169698329</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.006759572874372045</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.06883416327586214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1648676310822451</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T12" t="n">
         <v>3.248606501539229</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="C9" t="n">
-        <v>340.65939</v>
-      </c>
-      <c r="D9" t="n">
-        <v>99.188057</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.3487647357964</v>
-      </c>
-      <c r="G9" t="n">
-        <v>441.21029890854</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.02876423272774328</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0001643060434849185</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001237738812926141</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.107651087122964</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="M9" t="n">
-        <v>340.6601397504382</v>
-      </c>
-      <c r="N9" t="n">
-        <v>99.18804608732997</v>
-      </c>
-      <c r="O9" t="n">
-        <v>44.58464989712353</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.006468745362605588</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.04872990083878345</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.1617186340651398</v>
-      </c>
-      <c r="S9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4689999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>356.26501</v>
+      </c>
+      <c r="D13" t="n">
+        <v>102.85373</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4689999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.4563617403476</v>
+      </c>
+      <c r="G13" t="n">
+        <v>457.5160188606</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02885302919950098</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0001692270424838765</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.001917613845561901</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.230676062096914</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4689999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>356.2651554424828</v>
+      </c>
+      <c r="N13" t="n">
+        <v>102.8537186840326</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44.72228470361704</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.006662485585294466</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.07549664886115662</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1665621396323617</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T13" t="n">
         <v>5.408119403133058</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="C10" t="n">
-        <v>342.96631</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99.800995</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.364670395535601</v>
-      </c>
-      <c r="G10" t="n">
-        <v>443.9367819789</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.02879496417759991</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.0001688741012494819</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.001406612914175623</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.118880518280048</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="M10" t="n">
-        <v>342.9670648276924</v>
-      </c>
-      <c r="N10" t="n">
-        <v>99.80098401989453</v>
-      </c>
-      <c r="O10" t="n">
-        <v>44.63228373966881</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.006648590253602227</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.05537849109238568</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1621607378927373</v>
-      </c>
-      <c r="S10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5289999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>363.72858</v>
+      </c>
+      <c r="D14" t="n">
+        <v>103.91642</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5289999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.5078212642408</v>
+      </c>
+      <c r="G14" t="n">
+        <v>462.2430977724</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02886239828701478</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0002578195861922306</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.002175433431754132</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.296993103203843</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5289999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>363.7287284894285</v>
+      </c>
+      <c r="N14" t="n">
+        <v>103.9164085671155</v>
+      </c>
+      <c r="O14" t="n">
+        <v>44.73680681830759</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.01015038289034674</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.08564703175150336</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1691730481724457</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Impulse (lbf*s)</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T14" t="n">
         <v>280.2944475423513</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="C11" t="n">
-        <v>346.76593</v>
-      </c>
-      <c r="D11" t="n">
-        <v>100.67264</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.3908678635268</v>
-      </c>
-      <c r="G11" t="n">
-        <v>447.8140507008</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.02882011964259153</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.000170080830607604</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.001576693744783227</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4.14831294164888</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="M11" t="n">
-        <v>346.7666931902</v>
-      </c>
-      <c r="N11" t="n">
-        <v>100.6726289239962</v>
-      </c>
-      <c r="O11" t="n">
-        <v>44.67127478838777</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.006696099309104432</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.06207459040149011</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1633194953440106</v>
-      </c>
-      <c r="S11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="C15" t="n">
+        <v>373.09683</v>
+      </c>
+      <c r="D15" t="n">
+        <v>105.99204</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.572413099610801</v>
+      </c>
+      <c r="G15" t="n">
+        <v>471.4759121688</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.02886101433487755</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0001800970642267529</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.002355530495980885</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.392611322603726</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M15" t="n">
+        <v>373.0969823139454</v>
+      </c>
+      <c r="N15" t="n">
+        <v>105.9920283387558</v>
+      </c>
+      <c r="O15" t="n">
+        <v>44.73466168820464</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.007090439428313684</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.09273747117981704</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1729375470320409</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T15" t="n">
         <v>1092.014030435683</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.4289999999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>351.37979</v>
-      </c>
-      <c r="D12" t="n">
-        <v>101.42487</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4289999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.4226793209004</v>
-      </c>
-      <c r="G12" t="n">
-        <v>451.1601352314</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.0288396143833411</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0001716930582947985</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.001748386803078025</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.187635568165818</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4289999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>351.3805633447523</v>
-      </c>
-      <c r="N12" t="n">
-        <v>101.4248588412358</v>
-      </c>
-      <c r="O12" t="n">
-        <v>44.70149169698329</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.006759572874372045</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.06883416327586214</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1648676310822451</v>
-      </c>
-      <c r="S12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="C16" t="n">
+        <v>379.60562</v>
+      </c>
+      <c r="D16" t="n">
+        <v>107.29851</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.6172896445512</v>
+      </c>
+      <c r="G16" t="n">
+        <v>477.2873781521999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.0288529510122345</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.0001826339697848102</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.002538164465765695</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.454487067922196</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="M16" t="n">
+        <v>379.6057749711094</v>
+      </c>
+      <c r="N16" t="n">
+        <v>107.2984981950179</v>
+      </c>
+      <c r="O16" t="n">
+        <v>44.72216351311162</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.007190317653824957</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.09992778883364201</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1753736013128037</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>C* (ft/s)</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>5102.034198575786</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.4689999999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>356.26501</v>
-      </c>
-      <c r="D13" t="n">
-        <v>102.85373</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4689999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.4563617403476</v>
-      </c>
-      <c r="G13" t="n">
-        <v>457.5160188606</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.02885302919950098</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0001692270424838765</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.001917613845561901</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.230676062096914</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4689999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>356.2657940965352</v>
-      </c>
-      <c r="N13" t="n">
-        <v>102.8537186840326</v>
-      </c>
-      <c r="O13" t="n">
-        <v>44.72228470361704</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.006662485585294466</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.07549664886115662</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.1665621396323617</v>
-      </c>
-      <c r="S13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="C17" t="n">
+        <v>387.612</v>
+      </c>
+      <c r="D17" t="n">
+        <v>108.59851</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.67249171312</v>
+      </c>
+      <c r="G17" t="n">
+        <v>483.0700641522</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02883785703279348</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0001858903673599537</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.002724054833125649</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.533911399023257</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="M17" t="n">
+        <v>387.6121582396532</v>
+      </c>
+      <c r="N17" t="n">
+        <v>108.5984980519919</v>
+      </c>
+      <c r="O17" t="n">
+        <v>44.69876779818669</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.007318522351998114</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1072463111856401</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1785005451706855</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>363.7621686994284</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5289999999999999</v>
-      </c>
-      <c r="C14" t="n">
-        <v>363.72858</v>
-      </c>
-      <c r="D14" t="n">
-        <v>103.91642</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5289999999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.5078212642408</v>
-      </c>
-      <c r="G14" t="n">
-        <v>462.2430977724</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.02886239828701478</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0002578195861922306</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.002175433431754132</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.296993103203843</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5289999999999999</v>
-      </c>
-      <c r="M14" t="n">
-        <v>363.7293805229572</v>
-      </c>
-      <c r="N14" t="n">
-        <v>103.9164085671155</v>
-      </c>
-      <c r="O14" t="n">
-        <v>44.73680681830759</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.01015038289034674</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.08564703175150336</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.1691730481724457</v>
-      </c>
-      <c r="S14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6920000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>395.34698</v>
+      </c>
+      <c r="D18" t="n">
+        <v>109.89851</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6920000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.7258225438248</v>
+      </c>
+      <c r="G18" t="n">
+        <v>488.8527501522</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.02881601694565242</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0001844198117902966</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.002908474644915946</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.610495294757411</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6920000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>395.3471413974</v>
+      </c>
+      <c r="N18" t="n">
+        <v>109.8984979089659</v>
+      </c>
+      <c r="O18" t="n">
+        <v>44.66491559541378</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.007260626432165156</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1145069376178053</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1815156608041287</v>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Average Burnrate (in/s) (using full fire)</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>0.1675189279693448</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="C15" t="n">
-        <v>373.09683</v>
-      </c>
-      <c r="D15" t="n">
-        <v>105.99204</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.572413099610801</v>
-      </c>
-      <c r="G15" t="n">
-        <v>471.4759121688</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.02886101433487755</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0001800970642267529</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.002355530495980885</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.392611322603726</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="M15" t="n">
-        <v>373.0976511413513</v>
-      </c>
-      <c r="N15" t="n">
-        <v>105.9920283387558</v>
-      </c>
-      <c r="O15" t="n">
-        <v>44.73466168820464</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.007090439428313684</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.09273747117981704</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.1729375470320409</v>
-      </c>
-      <c r="S15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7320000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>404.57465</v>
+      </c>
+      <c r="D19" t="n">
+        <v>111.49204</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7320000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.789445113834</v>
+      </c>
+      <c r="G19" t="n">
+        <v>495.9411221688</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0287866832019797</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0001881773710304289</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.003096652015946375</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.704434275760719</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7320000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>404.5748151645262</v>
+      </c>
+      <c r="N19" t="n">
+        <v>111.4920277336458</v>
+      </c>
+      <c r="O19" t="n">
+        <v>44.61944820178646</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.007408561915205091</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1219154995330104</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1852140478801271</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (psig)</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T19" t="n">
         <v>471.1705377582196</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="C16" t="n">
-        <v>379.60562</v>
-      </c>
-      <c r="D16" t="n">
-        <v>107.29851</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.6172896445512</v>
-      </c>
-      <c r="G16" t="n">
-        <v>477.2873781521999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0288529510122345</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0001826339697848102</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.002538164465765695</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.454487067922196</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="M16" t="n">
-        <v>379.6064554664169</v>
-      </c>
-      <c r="N16" t="n">
-        <v>107.2984981950179</v>
-      </c>
-      <c r="O16" t="n">
-        <v>44.72216351311162</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.007190317653824957</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.09992778883364201</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1753736013128037</v>
-      </c>
-      <c r="S16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7730000000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>411.76682</v>
+      </c>
+      <c r="D20" t="n">
+        <v>112.91592</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7730000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.8390333998632</v>
+      </c>
+      <c r="G20" t="n">
+        <v>502.2748536624</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0287486129137506</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0001957538031542079</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.003292405819100583</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.774483003761163</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7730000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>411.766988100675</v>
+      </c>
+      <c r="N20" t="n">
+        <v>112.9159075769905</v>
+      </c>
+      <c r="O20" t="n">
+        <v>44.56043913701346</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.007706846805561479</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1296223463385719</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1879718733063774</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (in/s)</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T20" t="n">
         <v>0.2129182017132888</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="C17" t="n">
-        <v>387.612</v>
-      </c>
-      <c r="D17" t="n">
-        <v>108.59851</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.67249171312</v>
-      </c>
-      <c r="G17" t="n">
-        <v>483.0700641522</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.02883785703279348</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0001858903673599537</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.002724054833125649</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.533911399023257</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.652</v>
-      </c>
-      <c r="M17" t="n">
-        <v>387.6128530874986</v>
-      </c>
-      <c r="N17" t="n">
-        <v>108.5984980519919</v>
-      </c>
-      <c r="O17" t="n">
-        <v>44.69876779818669</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.007318522351998114</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.1072463111856401</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.1785005451706855</v>
-      </c>
-      <c r="S17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.8140000000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>418.68759</v>
+      </c>
+      <c r="D21" t="n">
+        <v>114.26816</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8140000000000002</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.8867504480284</v>
+      </c>
+      <c r="G21" t="n">
+        <v>508.2899146752</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02870213904278532</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0001985079117660905</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.003490913730866674</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.841656384538788</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8140000000000002</v>
+      </c>
+      <c r="M21" t="n">
+        <v>418.6877609260266</v>
+      </c>
+      <c r="N21" t="n">
+        <v>114.268147428217</v>
+      </c>
+      <c r="O21" t="n">
+        <v>44.48840449294828</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.007815276337022158</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.137437622675594</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1906164960249305</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>ISP (sec)</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T21" t="n">
         <v>183.7369756824667</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.6920000000000001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>395.34698</v>
-      </c>
-      <c r="D18" t="n">
-        <v>109.89851</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.6920000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.7258225438248</v>
-      </c>
-      <c r="G18" t="n">
-        <v>488.8527501522</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02881601694565242</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.0001844198117902966</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.002908474644915946</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.610495294757411</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6920000000000001</v>
-      </c>
-      <c r="M18" t="n">
-        <v>395.3478501112613</v>
-      </c>
-      <c r="N18" t="n">
-        <v>109.8984979089659</v>
-      </c>
-      <c r="O18" t="n">
-        <v>44.66491559541378</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.007260626432165156</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1145069376178053</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.1815156608041287</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.7320000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>404.57465</v>
-      </c>
-      <c r="D19" t="n">
-        <v>111.49204</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7320000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.789445113834</v>
-      </c>
-      <c r="G19" t="n">
-        <v>495.9411221688</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.0287866832019797</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.0001881773710304289</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.003096652015946375</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.704434275760719</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7320000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>404.5755404202557</v>
-      </c>
-      <c r="N19" t="n">
-        <v>111.4920277336458</v>
-      </c>
-      <c r="O19" t="n">
-        <v>44.61944820178646</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.007408561915205091</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1219154995330104</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.1852140478801271</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.7730000000000001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>411.76682</v>
-      </c>
-      <c r="D20" t="n">
-        <v>112.91592</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.7730000000000001</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.8390333998632</v>
-      </c>
-      <c r="G20" t="n">
-        <v>502.2748536624</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0287486129137506</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0001957538031542079</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.003292405819100583</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.774483003761163</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7730000000000001</v>
-      </c>
-      <c r="M20" t="n">
-        <v>411.7677262493589</v>
-      </c>
-      <c r="N20" t="n">
-        <v>112.9159075769905</v>
-      </c>
-      <c r="O20" t="n">
-        <v>44.56043913701346</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.007706846805561479</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1296223463385719</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.1879718733063774</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.8140000000000002</v>
-      </c>
-      <c r="C21" t="n">
-        <v>418.68759</v>
-      </c>
-      <c r="D21" t="n">
-        <v>114.26816</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8140000000000002</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.8867504480284</v>
-      </c>
-      <c r="G21" t="n">
-        <v>508.2899146752</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02870213904278532</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.0001985079117660905</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.003490913730866674</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.841656384538788</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.8140000000000002</v>
-      </c>
-      <c r="M21" t="n">
-        <v>418.6885114811431</v>
-      </c>
-      <c r="N21" t="n">
-        <v>114.268147428217</v>
-      </c>
-      <c r="O21" t="n">
-        <v>44.48840449294828</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.007815276337022158</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.137437622675594</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.1906164960249305</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -6394,7 +6442,7 @@
         <v>0.8560000000000002</v>
       </c>
       <c r="M22" t="n">
-        <v>425.4735664142019</v>
+        <v>425.4728036959676</v>
       </c>
       <c r="N22" t="n">
         <v>115.3427773099863</v>
@@ -6452,7 +6500,7 @@
         <v>0.9000000000000002</v>
       </c>
       <c r="M23" t="n">
-        <v>431.987250750008</v>
+        <v>431.986476355124</v>
       </c>
       <c r="N23" t="n">
         <v>116.4084371927423</v>
@@ -6510,7 +6558,7 @@
         <v>0.9600000000000002</v>
       </c>
       <c r="M24" t="n">
-        <v>440.129358669771</v>
+        <v>440.1285696790703</v>
       </c>
       <c r="N24" t="n">
         <v>117.3497370891805</v>
@@ -6568,7 +6616,7 @@
         <v>1.001</v>
       </c>
       <c r="M25" t="n">
-        <v>450.4765114425625</v>
+        <v>450.4757039032075</v>
       </c>
       <c r="N25" t="n">
         <v>119.1492368911995</v>
@@ -6626,7 +6674,7 @@
         <v>1.041</v>
       </c>
       <c r="M26" t="n">
-        <v>455.1922218212523</v>
+        <v>455.1914058283562</v>
       </c>
       <c r="N26" t="n">
         <v>120.0731267895531</v>
@@ -6684,7 +6732,7 @@
         <v>1.082</v>
       </c>
       <c r="M27" t="n">
-        <v>462.6558382477402</v>
+        <v>462.6550088753141</v>
       </c>
       <c r="N27" t="n">
         <v>120.8766067011543</v>
@@ -6742,7 +6790,7 @@
         <v>1.123</v>
       </c>
       <c r="M28" t="n">
-        <v>469.1694925834802</v>
+        <v>469.1686515344581</v>
       </c>
       <c r="N28" t="n">
         <v>122.0825765684735</v>
@@ -6800,7 +6848,7 @@
         <v>1.164</v>
       </c>
       <c r="M29" t="n">
-        <v>474.8689351272417</v>
+        <v>474.8680838612071</v>
       </c>
       <c r="N29" t="n">
         <v>123.2213764431827</v>
@@ -6858,7 +6906,7 @@
         <v>1.204</v>
       </c>
       <c r="M30" t="n">
-        <v>477.7186713991555</v>
+        <v>477.7178150245878</v>
       </c>
       <c r="N30" t="n">
         <v>123.7402863860922</v>
@@ -6916,7 +6964,7 @@
         <v>1.244</v>
       </c>
       <c r="M31" t="n">
-        <v>484.3680360335769</v>
+        <v>484.3671677391343</v>
       </c>
       <c r="N31" t="n">
         <v>124.1895363366657</v>
@@ -6974,7 +7022,7 @@
         <v>1.285</v>
       </c>
       <c r="M32" t="n">
-        <v>486.9463817081939</v>
+        <v>486.9455087917221</v>
       </c>
       <c r="N32" t="n">
         <v>124.9129162570794</v>
@@ -7032,7 +7080,7 @@
         <v>1.326</v>
       </c>
       <c r="M33" t="n">
-        <v>492.2387233559771</v>
+        <v>492.2378409522755</v>
       </c>
       <c r="N33" t="n">
         <v>125.4940161931468</v>
@@ -7090,7 +7138,7 @@
         <v>1.386</v>
       </c>
       <c r="M34" t="n">
-        <v>497.6667753024419</v>
+        <v>497.6658831682317</v>
       </c>
       <c r="N34" t="n">
         <v>125.9865461389587</v>
@@ -7148,7 +7196,7 @@
         <v>1.427</v>
       </c>
       <c r="M35" t="n">
-        <v>501.1121228852217</v>
+        <v>501.1112245747656</v>
       </c>
       <c r="N35" t="n">
         <v>127.1353060125721</v>
@@ -7206,7 +7254,7 @@
         <v>1.467</v>
       </c>
       <c r="M36" t="n">
-        <v>505.6732029235895</v>
+        <v>505.6722964367877</v>
       </c>
       <c r="N36" t="n">
         <v>127.0114260262014</v>
@@ -7264,7 +7312,7 @@
         <v>1.508</v>
       </c>
       <c r="M37" t="n">
-        <v>510.9655445713727</v>
+        <v>510.9646285973412</v>
       </c>
       <c r="N37" t="n">
         <v>127.7601859438228</v>
@@ -7322,7 +7370,7 @@
         <v>1.551</v>
       </c>
       <c r="M38" t="n">
-        <v>513.2724896486708</v>
+        <v>513.2715695391319</v>
       </c>
       <c r="N38" t="n">
         <v>128.3616758776469</v>
@@ -7380,7 +7428,7 @@
         <v>1.592</v>
       </c>
       <c r="M39" t="n">
-        <v>515.7151250246063</v>
+        <v>515.7142005363171</v>
       </c>
       <c r="N39" t="n">
         <v>128.5213758600767</v>
@@ -7438,7 +7486,7 @@
         <v>1.633</v>
       </c>
       <c r="M40" t="n">
-        <v>516.3935965178374</v>
+        <v>516.3926708132973</v>
       </c>
       <c r="N40" t="n">
         <v>128.4606758667549</v>
@@ -7496,7 +7544,7 @@
         <v>1.673</v>
       </c>
       <c r="M41" t="n">
-        <v>520.4646454777079</v>
+        <v>520.4637124752684</v>
       </c>
       <c r="N41" t="n">
         <v>128.3741158762782</v>
@@ -7554,7 +7602,7 @@
         <v>1.714</v>
       </c>
       <c r="M42" t="n">
-        <v>523.9929132429847</v>
+        <v>523.9919739156537</v>
       </c>
       <c r="N42" t="n">
         <v>128.5860558529606</v>
@@ -7612,7 +7660,7 @@
         <v>1.754999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>527.6568613068771</v>
+        <v>527.6559154114294</v>
       </c>
       <c r="N43" t="n">
         <v>128.9666458110881</v>
@@ -7670,7 +7718,7 @@
         <v>1.815</v>
       </c>
       <c r="M44" t="n">
-        <v>529.5566454880649</v>
+        <v>529.5556961870001</v>
       </c>
       <c r="N44" t="n">
         <v>129.403475763028</v>
@@ -7728,7 +7776,7 @@
         <v>1.855999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>532.606702200859</v>
+        <v>532.60574743216</v>
       </c>
       <c r="N45" t="n">
         <v>129.2208857831166</v>
@@ -7786,7 +7834,7 @@
         <v>1.896999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>531.7279202667696</v>
+        <v>531.7269670734046</v>
       </c>
       <c r="N46" t="n">
         <v>129.4029657630842</v>
@@ -7844,7 +7892,7 @@
         <v>1.937999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>502.0092548596972</v>
+        <v>502.008354941012</v>
       </c>
       <c r="N47" t="n">
         <v>129.1571957901238</v>
@@ -7902,7 +7950,7 @@
         <v>1.978999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>440.5364295656832</v>
+        <v>440.5356398452535</v>
       </c>
       <c r="N48" t="n">
         <v>123.231826442033</v>
@@ -7960,7 +8008,7 @@
         <v>2.020999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>391.1410908527094</v>
+        <v>391.1403896800263</v>
       </c>
       <c r="N49" t="n">
         <v>105.6074483810673</v>
@@ -8018,7 +8066,7 @@
         <v>2.061999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>361.0153545497249</v>
+        <v>361.0147073814505</v>
       </c>
       <c r="N50" t="n">
         <v>91.3586939487154</v>
@@ -8076,7 +8124,7 @@
         <v>2.102999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>350.2949309554108</v>
+        <v>350.2943030049286</v>
       </c>
       <c r="N51" t="n">
         <v>84.90844565837179</v>
@@ -8134,7 +8182,7 @@
         <v>2.142999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>345.1382696062431</v>
+        <v>345.1376508997654</v>
       </c>
       <c r="N52" t="n">
         <v>81.50496503282277</v>
@@ -8192,7 +8240,7 @@
         <v>2.185999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>341.0672206463725</v>
+        <v>341.0666092377944</v>
       </c>
       <c r="N53" t="n">
         <v>80.22834617327638</v>
@@ -8250,7 +8298,7 @@
         <v>2.245999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>334.2821357132477</v>
+        <v>334.2815364678411</v>
       </c>
       <c r="N54" t="n">
         <v>79.00845230748912</v>
@@ -8308,7 +8356,7 @@
         <v>2.286999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>328.4351428447463</v>
+        <v>328.4345540808559</v>
       </c>
       <c r="N55" t="n">
         <v>76.74675655632092</v>
@@ -8366,7 +8414,7 @@
         <v>2.327999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>323.1546412230214</v>
+        <v>323.154061925136</v>
       </c>
       <c r="N56" t="n">
         <v>75.69850067165005</v>
@@ -8424,7 +8472,7 @@
         <v>2.368999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>319.2193025618324</v>
+        <v>319.2187303185675</v>
       </c>
       <c r="N57" t="n">
         <v>74.56069079683191</v>
@@ -8482,7 +8530,7 @@
         <v>2.408999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>312.8412985246418</v>
+        <v>312.8407377148015</v>
       </c>
       <c r="N58" t="n">
         <v>73.33680693148362</v>
@@ -8540,7 +8588,7 @@
         <v>2.449999999999999</v>
       </c>
       <c r="M59" t="n">
-        <v>308.6345592661339</v>
+        <v>308.634005997436</v>
       </c>
       <c r="N59" t="n">
         <v>71.94277908485458</v>
@@ -8598,7 +8646,7 @@
         <v>2.490999999999999</v>
       </c>
       <c r="M60" t="n">
-        <v>304.4278200076259</v>
+        <v>304.4272742800703</v>
       </c>
       <c r="N60" t="n">
         <v>70.66416922552725</v>
@@ -8656,7 +8704,7 @@
         <v>2.531999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>293.3002955173337</v>
+        <v>293.2997697373531</v>
       </c>
       <c r="N61" t="n">
         <v>69.86516531343366</v>
@@ -8714,7 +8762,7 @@
         <v>2.572999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>267.5169787714725</v>
+        <v>267.5164992115331</v>
       </c>
       <c r="N62" t="n">
         <v>66.89004564075637</v>
@@ -8772,7 +8820,7 @@
         <v>2.613999999999999</v>
       </c>
       <c r="M63" t="n">
-        <v>227.7564412634933</v>
+        <v>227.7560329796316</v>
       </c>
       <c r="N63" t="n">
         <v>61.51790323179954</v>
@@ -8830,7 +8878,7 @@
         <v>2.672999999999999</v>
       </c>
       <c r="M64" t="n">
-        <v>182.2964112116425</v>
+        <v>182.2960844209607</v>
       </c>
       <c r="N64" t="n">
         <v>50.60546743238586</v>
@@ -8888,7 +8936,7 @@
         <v>2.713999999999999</v>
       </c>
       <c r="M65" t="n">
-        <v>124.6708643850081</v>
+        <v>124.6706408958209</v>
       </c>
       <c r="N65" t="n">
         <v>35.00049214924543</v>
@@ -8946,7 +8994,7 @@
         <v>2.753999999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>89.88365882271165</v>
+        <v>89.88349769423985</v>
       </c>
       <c r="N66" t="n">
         <v>24.28755832788254</v>
@@ -9004,7 +9052,7 @@
         <v>2.794999999999999</v>
       </c>
       <c r="M67" t="n">
-        <v>59.89362181838427</v>
+        <v>59.89351445106211</v>
       </c>
       <c r="N67" t="n">
         <v>17.60895306266277</v>
@@ -9062,7 +9110,7 @@
         <v>2.835999999999999</v>
       </c>
       <c r="M68" t="n">
-        <v>35.87444195516805</v>
+        <v>35.87437764543606</v>
       </c>
       <c r="N68" t="n">
         <v>10.4099488546973</v>
@@ -9120,7 +9168,7 @@
         <v>2.879999999999999</v>
       </c>
       <c r="M69" t="n">
-        <v>20.94727010232636</v>
+        <v>20.947232551545</v>
       </c>
       <c r="N69" t="n">
         <v>6.176118620503355</v>
@@ -9178,7 +9226,7 @@
         <v>2.920999999999998</v>
       </c>
       <c r="M70" t="n">
-        <v>11.04105729998871</v>
+        <v>11.04103750741781</v>
       </c>
       <c r="N70" t="n">
         <v>1.207462567154954</v>
@@ -9236,7 +9284,7 @@
         <v>2.960999999999999</v>
       </c>
       <c r="M71" t="n">
-        <v>7.105712338785753</v>
+        <v>7.105699600846675</v>
       </c>
       <c r="N71" t="n">
         <v>-1.098009779196951</v>
@@ -9294,7 +9342,7 @@
         <v>3.001999999999998</v>
       </c>
       <c r="M72" t="n">
-        <v>5.748696552163421</v>
+        <v>5.748686246856512</v>
       </c>
       <c r="N72" t="n">
         <v>-1.86069639528616</v>
@@ -9463,7 +9511,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>2.080596979134202</v>
+        <v>2.080593249386035</v>
       </c>
       <c r="N2" t="n">
         <v>2.621890211539608</v>
@@ -9481,1205 +9529,1229 @@
         <v>0</v>
       </c>
       <c r="S2" t="inlineStr">
+        <is>
+          <t>Throat Area (mm^2)</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>134.3914911436338</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="C3" t="n">
+        <v>231.1443</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.8069651</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.593684473868</v>
+      </c>
+      <c r="G3" t="n">
+        <v>12.485998297122</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.02841260032616762</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0001113916849080732</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.0001113916849080732</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.716870363611541</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="M3" t="n">
+        <v>231.1443943629038</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.8069647911777</v>
+      </c>
+      <c r="O3" t="n">
+        <v>44.03961858462082</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.004385501773999332</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.004385501773999332</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1069634579024227</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Throat Diameter (mm)</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>13.081</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>302.52316</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66.90746300000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.0858245826416</v>
+      </c>
+      <c r="G4" t="n">
+        <v>297.6191150658601</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.02849692804198087</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0002084940810800518</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.0003198857659881249</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.533797984407657</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>302.5232835027809</v>
+      </c>
+      <c r="N4" t="n">
+        <v>66.90745563884094</v>
+      </c>
+      <c r="O4" t="n">
+        <v>44.17032680554728</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.008208432821529745</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01259393459552908</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1391259800259279</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Throat Area (in^2)</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2083072278870882</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="C5" t="n">
+        <v>311.07236</v>
+      </c>
+      <c r="D5" t="n">
+        <v>89.69154399999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.1447692648336</v>
+      </c>
+      <c r="G5" t="n">
+        <v>398.96771985168</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.02855160588820399</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.000148344212581971</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.000468229978570096</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.618151526389536</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.141</v>
+      </c>
+      <c r="M5" t="n">
+        <v>311.0724869929269</v>
+      </c>
+      <c r="N5" t="n">
+        <v>89.69153413213633</v>
+      </c>
+      <c r="O5" t="n">
+        <v>44.25507763669444</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.005840326483773457</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01843426107930253</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1424469874091087</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Throat Diameter (in)</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>0.515</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="C6" t="n">
+        <v>313.37927</v>
+      </c>
+      <c r="D6" t="n">
+        <v>91.334328</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.1606748556252</v>
+      </c>
+      <c r="G6" t="n">
+        <v>406.27518449616</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.02860201412188751</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0001488227715078501</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.000617052750077946</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.629823695313416</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="M6" t="n">
+        <v>313.3793979347054</v>
+      </c>
+      <c r="N6" t="n">
+        <v>91.33431795139724</v>
+      </c>
+      <c r="O6" t="n">
+        <v>44.33321055516942</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.005859167396541209</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.02429342847584375</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1429065218668587</v>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>Burn Time (sec)</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="T6" t="n">
         <v>2.968999999999998</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="C3" t="n">
-        <v>231.1443</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.8069651</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.593684473868</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.485998297122</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.02841260032616762</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0001113916849080732</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.0001113916849080732</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.716870363611541</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="M3" t="n">
-        <v>231.144808720867</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.8069647911777</v>
-      </c>
-      <c r="O3" t="n">
-        <v>44.03961858462082</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.004385501773999332</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.004385501773999332</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1069634579024227</v>
-      </c>
-      <c r="S3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="C7" t="n">
+        <v>317.85742</v>
+      </c>
+      <c r="D7" t="n">
+        <v>91.548759</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.1915506251192</v>
+      </c>
+      <c r="G7" t="n">
+        <v>407.22902075898</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.02864841298368229</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0001503339244785882</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.0007673866745565342</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.666681084843615</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="M7" t="n">
+        <v>317.857549762876</v>
+      </c>
+      <c r="N7" t="n">
+        <v>91.54874892780555</v>
+      </c>
+      <c r="O7" t="n">
+        <v>44.4051289347878</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.005918661640114467</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.03021209011595821</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.1443576009784016</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>Impulse (N*s)</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="T7" t="n">
         <v>1287.209403326247</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>302.52316</v>
-      </c>
-      <c r="D4" t="n">
-        <v>66.90746300000001</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2.0858245826416</v>
-      </c>
-      <c r="G4" t="n">
-        <v>297.6191150658601</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.02849692804198087</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0002084940810800518</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.0003198857659881249</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.533797984407657</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>302.5238258171724</v>
-      </c>
-      <c r="N4" t="n">
-        <v>66.90745563884094</v>
-      </c>
-      <c r="O4" t="n">
-        <v>44.17032680554728</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.008208432821529745</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.01259393459552908</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.1391259800259279</v>
-      </c>
-      <c r="S4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="C8" t="n">
+        <v>321.38562</v>
+      </c>
+      <c r="D8" t="n">
+        <v>92.435822</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.2158767173512</v>
+      </c>
+      <c r="G8" t="n">
+        <v>411.17487213684</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.02869054766773843</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.0001513973300078884</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.0009187840045644226</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.692617805070451</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="M8" t="n">
+        <v>321.3857512032369</v>
+      </c>
+      <c r="N8" t="n">
+        <v>92.43581183021087</v>
+      </c>
+      <c r="O8" t="n">
+        <v>44.47043782569234</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.005960528022143567</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.03617261813810178</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.1453787322474041</v>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>Full Pressure Integral (MPa*s)</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="T8" t="n">
         <v>7.965040834724157</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="C5" t="n">
-        <v>311.07236</v>
-      </c>
-      <c r="D5" t="n">
-        <v>89.69154399999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.1447692648336</v>
-      </c>
-      <c r="G5" t="n">
-        <v>398.96771985168</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.02855160588820399</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.000148344212581971</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.000468229978570096</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.618151526389536</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="M5" t="n">
-        <v>311.0730446329357</v>
-      </c>
-      <c r="N5" t="n">
-        <v>89.69153413213633</v>
-      </c>
-      <c r="O5" t="n">
-        <v>44.25507763669444</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.005840326483773457</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.01843426107930253</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1424469874091087</v>
-      </c>
-      <c r="S5" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="C9" t="n">
+        <v>325.45667</v>
+      </c>
+      <c r="D9" t="n">
+        <v>93.12039900000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.2439456300492</v>
+      </c>
+      <c r="G9" t="n">
+        <v>414.22002123978</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0287283809493879</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001527184159754961</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.001071502420539919</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.724839414036492</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="M9" t="n">
+        <v>325.4568028652121</v>
+      </c>
+      <c r="N9" t="n">
+        <v>93.12038875489371</v>
+      </c>
+      <c r="O9" t="n">
+        <v>44.52907952953218</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.006012539308796879</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.04218515744689865</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.1466473002145581</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>C* (m/s)</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="T9" t="n">
         <v>1547.478234644485</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="C6" t="n">
-        <v>313.37927</v>
-      </c>
-      <c r="D6" t="n">
-        <v>91.334328</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.1606748556252</v>
-      </c>
-      <c r="G6" t="n">
-        <v>406.27518449616</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.02860201412188751</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0001488227715078501</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.000617052750077946</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.629823695313416</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="M6" t="n">
-        <v>313.3799597101678</v>
-      </c>
-      <c r="N6" t="n">
-        <v>91.33431795139724</v>
-      </c>
-      <c r="O6" t="n">
-        <v>44.33321055516942</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.005859167396541209</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.02429342847584375</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.1429065218668587</v>
-      </c>
-      <c r="S6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="C10" t="n">
+        <v>330.47763</v>
+      </c>
+      <c r="D10" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.2785639442188</v>
+      </c>
+      <c r="G10" t="n">
+        <v>420.35679</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.02876188054535236</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0001544835351474083</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.001225985955687327</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.767891101156303</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="M10" t="n">
+        <v>330.4777649149809</v>
+      </c>
+      <c r="N10" t="n">
+        <v>94.49998960311</v>
+      </c>
+      <c r="O10" t="n">
+        <v>44.58100400712586</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.006082032227106981</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.04826718967400563</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1483422494416338</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (MPa)</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="T10" t="n">
         <v>2.682735208731614</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="C7" t="n">
-        <v>317.85742</v>
-      </c>
-      <c r="D7" t="n">
-        <v>91.548759</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2.1915506251192</v>
-      </c>
-      <c r="G7" t="n">
-        <v>407.22902075898</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.02864841298368229</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.0001503339244785882</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.0007673866745565342</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.666681084843615</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.223</v>
-      </c>
-      <c r="M7" t="n">
-        <v>317.8581195660385</v>
-      </c>
-      <c r="N7" t="n">
-        <v>91.54874892780555</v>
-      </c>
-      <c r="O7" t="n">
-        <v>44.4051289347878</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.005918661640114467</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.03021209011595821</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.1443576009784016</v>
-      </c>
-      <c r="S7" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="C11" t="n">
+        <v>334.95575</v>
+      </c>
+      <c r="D11" t="n">
+        <v>95.815918</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.30943950687</v>
+      </c>
+      <c r="G11" t="n">
+        <v>426.21028276596</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02879083875878197</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.000155994317752375</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.001381980273439702</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.804739457375001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="M11" t="n">
+        <v>334.9558867431393</v>
+      </c>
+      <c r="N11" t="n">
+        <v>95.8159074583327</v>
+      </c>
+      <c r="O11" t="n">
+        <v>44.6258893277122</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.006141511889342778</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05440870156334841</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.1497929729107995</v>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>Average Burnrate (using full fire) (mm/s)</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="T11" t="n">
         <v>4.302532935072866</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="C8" t="n">
-        <v>321.38562</v>
-      </c>
-      <c r="D8" t="n">
-        <v>92.435822</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2.2158767173512</v>
-      </c>
-      <c r="G8" t="n">
-        <v>411.17487213684</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.02869054766773843</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.0001513973300078884</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0009187840045644226</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.692617805070451</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.264</v>
-      </c>
-      <c r="M8" t="n">
-        <v>321.3863273311833</v>
-      </c>
-      <c r="N8" t="n">
-        <v>92.43581183021087</v>
-      </c>
-      <c r="O8" t="n">
-        <v>44.47043782569234</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.005960528022143567</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.03617261813810178</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.1453787322474041</v>
-      </c>
-      <c r="S8" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4309999999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>340.92664</v>
+      </c>
+      <c r="D12" t="n">
+        <v>97.353233</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.4309999999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.3506073604064</v>
+      </c>
+      <c r="G12" t="n">
+        <v>433.04859809526</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.02881678861524217</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0001697276047654342</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.001551707878205136</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.857445562850779</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4309999999999999</v>
+      </c>
+      <c r="M12" t="n">
+        <v>340.9267791807098</v>
+      </c>
+      <c r="N12" t="n">
+        <v>97.35322228919732</v>
+      </c>
+      <c r="O12" t="n">
+        <v>44.66611168567007</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.006682192772375622</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.06109089433572404</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.1518680175539915</v>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (MPa)</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="T12" t="n">
         <v>3.546304583953522</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="C9" t="n">
-        <v>325.45667</v>
-      </c>
-      <c r="D9" t="n">
-        <v>93.12039900000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2.2439456300492</v>
-      </c>
-      <c r="G9" t="n">
-        <v>414.22002123978</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0287283809493879</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0001527184159754961</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.001071502420539919</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.724839414036492</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="M9" t="n">
-        <v>325.4573862910759</v>
-      </c>
-      <c r="N9" t="n">
-        <v>93.12038875489371</v>
-      </c>
-      <c r="O9" t="n">
-        <v>44.52907952953218</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.006012539308796879</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.04218515744689865</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.1466473002145581</v>
-      </c>
-      <c r="S9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4739999999999999</v>
+      </c>
+      <c r="C13" t="n">
+        <v>346.49039</v>
+      </c>
+      <c r="D13" t="n">
+        <v>98.996521</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4739999999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.3889680813564</v>
+      </c>
+      <c r="G13" t="n">
+        <v>440.35830464262</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02883676533420074</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0001679504955656127</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.001719658373770749</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.905825478270063</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4739999999999999</v>
+      </c>
+      <c r="M13" t="n">
+        <v>346.4905314520684</v>
+      </c>
+      <c r="N13" t="n">
+        <v>98.99651010840276</v>
+      </c>
+      <c r="O13" t="n">
+        <v>44.69707566198368</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.006612227805467726</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.06770312214119176</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1537727396620402</v>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (mm/s)</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="T13" t="n">
         <v>5.581836910624572</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="C10" t="n">
-        <v>330.47763</v>
-      </c>
-      <c r="D10" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2.2785639442188</v>
-      </c>
-      <c r="G10" t="n">
-        <v>420.35679</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.02876188054535236</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.0001544835351474083</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.001225985955687327</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.767891101156303</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="M10" t="n">
-        <v>330.4783573416063</v>
-      </c>
-      <c r="N10" t="n">
-        <v>94.49998960311</v>
-      </c>
-      <c r="O10" t="n">
-        <v>44.58100400712586</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.006082032227106981</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.04826718967400563</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.1483422494416338</v>
-      </c>
-      <c r="S10" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.5319999999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>356.53076</v>
+      </c>
+      <c r="D14" t="n">
+        <v>101.15472</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5319999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.4581940228176</v>
+      </c>
+      <c r="G14" t="n">
+        <v>449.9584485984</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02885503010791578</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0002319614496719084</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.001951619823442657</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.999335339170835</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.5319999999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>356.5309055509732</v>
+      </c>
+      <c r="N14" t="n">
+        <v>101.1547088709577</v>
+      </c>
+      <c r="O14" t="n">
+        <v>44.7253861178628</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.009132345469728003</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.07683546761091976</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.1574542322366897</v>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>Impulse (lbf*s)</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="T14" t="n">
         <v>289.3762587523703</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="C11" t="n">
-        <v>334.95575</v>
-      </c>
-      <c r="D11" t="n">
-        <v>95.815918</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.30943950687</v>
-      </c>
-      <c r="G11" t="n">
-        <v>426.21028276596</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.02879083875878197</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.000155994317752375</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.001381980273439702</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.804739457375001</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="M11" t="n">
-        <v>334.9564871974111</v>
-      </c>
-      <c r="N11" t="n">
-        <v>95.8159074583327</v>
-      </c>
-      <c r="O11" t="n">
-        <v>44.6258893277122</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.006141511889342778</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.05440870156334841</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.1497929729107995</v>
-      </c>
-      <c r="S11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="C15" t="n">
+        <v>366.30276</v>
+      </c>
+      <c r="D15" t="n">
+        <v>102.4199</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.5255696175376</v>
+      </c>
+      <c r="G15" t="n">
+        <v>455.586247578</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.02886150128751758</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.0001678982042589219</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.002119518027701579</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.095078152656627</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="M15" t="n">
+        <v>366.3029095403179</v>
+      </c>
+      <c r="N15" t="n">
+        <v>102.4198887317626</v>
+      </c>
+      <c r="O15" t="n">
+        <v>44.73541646630624</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.006610169091494179</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.08344563670241395</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.1612236363779067</v>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>Full Pressure Integral (psig*s)</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="T15" t="n">
         <v>1155.231503595463</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0.4309999999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>340.92664</v>
-      </c>
-      <c r="D12" t="n">
-        <v>97.353233</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.4309999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.3506073604064</v>
-      </c>
-      <c r="G12" t="n">
-        <v>433.04859809526</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.02881678861524217</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.0001697276047654342</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.001551707878205136</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.857445562850779</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4309999999999999</v>
-      </c>
-      <c r="M12" t="n">
-        <v>340.9273903386235</v>
-      </c>
-      <c r="N12" t="n">
-        <v>97.35322228919732</v>
-      </c>
-      <c r="O12" t="n">
-        <v>44.66611168567007</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.006682192772375622</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.06109089433572404</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.1518680175539915</v>
-      </c>
-      <c r="S12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="C16" t="n">
+        <v>374.30911</v>
+      </c>
+      <c r="D16" t="n">
+        <v>104.83035</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.5807714792636</v>
+      </c>
+      <c r="G16" t="n">
+        <v>466.308459477</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.02886226605313616</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.000171002728908638</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.002290520756610217</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.170798266064337</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="M16" t="n">
+        <v>374.3092628088494</v>
+      </c>
+      <c r="N16" t="n">
+        <v>104.8303384665649</v>
+      </c>
+      <c r="O16" t="n">
+        <v>44.73660185538581</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.006732394537405968</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.09017803123981991</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.1642047448147796</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>C* (ft/s)</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="T16" t="n">
         <v>5077.028328865798</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0.4739999999999999</v>
-      </c>
-      <c r="C13" t="n">
-        <v>346.49039</v>
-      </c>
-      <c r="D13" t="n">
-        <v>98.996521</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.4739999999999999</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2.3889680813564</v>
-      </c>
-      <c r="G13" t="n">
-        <v>440.35830464262</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.02883676533420074</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.0001679504955656127</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.001719658373770749</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.905825478270063</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.4739999999999999</v>
-      </c>
-      <c r="M13" t="n">
-        <v>346.4911525837696</v>
-      </c>
-      <c r="N13" t="n">
-        <v>98.99651010840276</v>
-      </c>
-      <c r="O13" t="n">
-        <v>44.69707566198368</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.006612227805467726</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.06770312214119176</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.1537727396620402</v>
-      </c>
-      <c r="S13" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="C17" t="n">
+        <v>384.07962</v>
+      </c>
+      <c r="D17" t="n">
+        <v>106.12587</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.6481368007912</v>
+      </c>
+      <c r="G17" t="n">
+        <v>472.0712174514001</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02885696622747926</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0001749012439469829</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0024654220005572</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.265883998706896</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="M17" t="n">
+        <v>384.0797767975859</v>
+      </c>
+      <c r="N17" t="n">
+        <v>106.1258583240318</v>
+      </c>
+      <c r="O17" t="n">
+        <v>44.72838710918816</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.006885879464317112</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.09706391070413702</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.1679482796174904</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>Average Pressure (using full fire) (psig)</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="T17" t="n">
         <v>389.0978456030527</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0.5319999999999999</v>
-      </c>
-      <c r="C14" t="n">
-        <v>356.53076</v>
-      </c>
-      <c r="D14" t="n">
-        <v>101.15472</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.5319999999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.4581940228176</v>
-      </c>
-      <c r="G14" t="n">
-        <v>449.9584485984</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.02885503010791578</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0002319614496719084</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.001951619823442657</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.999335339170835</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5319999999999999</v>
-      </c>
-      <c r="M14" t="n">
-        <v>356.5315446814191</v>
-      </c>
-      <c r="N14" t="n">
-        <v>101.1547088709577</v>
-      </c>
-      <c r="O14" t="n">
-        <v>44.7253861178628</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.009132345469728003</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.07683546761091976</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.1574542322366897</v>
-      </c>
-      <c r="S14" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>396.02133</v>
+      </c>
+      <c r="D18" t="n">
+        <v>108.09751</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.7304720252308</v>
+      </c>
+      <c r="G18" t="n">
+        <v>480.8415059322</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.02884510906582893</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.0001797702970001744</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.002645192297557374</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.384641390248153</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6960000000000001</v>
+      </c>
+      <c r="M18" t="n">
+        <v>396.0214916726982</v>
+      </c>
+      <c r="N18" t="n">
+        <v>108.0974981071119</v>
+      </c>
+      <c r="O18" t="n">
+        <v>44.71000847187294</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.007077574569926568</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.1041414852740636</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1726237699982088</v>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>Average Burnrate (in/s) (using full fire)</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="T18" t="n">
         <v>0.1693911519071123</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="C15" t="n">
-        <v>366.30276</v>
-      </c>
-      <c r="D15" t="n">
-        <v>102.4199</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2.5255696175376</v>
-      </c>
-      <c r="G15" t="n">
-        <v>455.586247578</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.02886150128751758</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.0001678982042589219</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.002119518027701579</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.095078152656627</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="M15" t="n">
-        <v>366.3035661884184</v>
-      </c>
-      <c r="N15" t="n">
-        <v>102.4198887317626</v>
-      </c>
-      <c r="O15" t="n">
-        <v>44.73541646630624</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.006610169091494179</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.08344563670241395</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.1612236363779067</v>
-      </c>
-      <c r="S15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>406.60602</v>
+      </c>
+      <c r="D19" t="n">
+        <v>110.81244</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.8034509224552</v>
+      </c>
+      <c r="G19" t="n">
+        <v>492.9181118568</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02882624292636143</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.0001840089661623492</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.002829201263719724</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.488023564935343</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.7370000000000001</v>
+      </c>
+      <c r="M19" t="n">
+        <v>406.6061859938175</v>
+      </c>
+      <c r="N19" t="n">
+        <v>110.8124278084154</v>
+      </c>
+      <c r="O19" t="n">
+        <v>44.68076589721328</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.007244451398708306</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1113859366727719</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.176693936553861</v>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>Average Pressure (using points above average) (psig)</t>
         </is>
       </c>
-      <c r="T15" t="n">
+      <c r="T19" t="n">
         <v>514.3479941581477</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="C16" t="n">
-        <v>374.30911</v>
-      </c>
-      <c r="D16" t="n">
-        <v>104.83035</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.5807714792636</v>
-      </c>
-      <c r="G16" t="n">
-        <v>466.308459477</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.02886226605313616</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.000171002728908638</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.002290520756610217</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4.170798266064337</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="M16" t="n">
-        <v>374.309933809434</v>
-      </c>
-      <c r="N16" t="n">
-        <v>104.8303384665649</v>
-      </c>
-      <c r="O16" t="n">
-        <v>44.73660185538581</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.006732394537405968</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.09017803123981991</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.1642047448147796</v>
-      </c>
-      <c r="S16" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.7790000000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>419.76904</v>
+      </c>
+      <c r="D20" t="n">
+        <v>112.45473</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7790000000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.8942067862304</v>
+      </c>
+      <c r="G20" t="n">
+        <v>500.2233790806</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.02879897945821836</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.0001940040783350489</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.003023205342054772</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.619144722263064</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.7790000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>419.7692113675204</v>
+      </c>
+      <c r="N20" t="n">
+        <v>112.4547176277306</v>
+      </c>
+      <c r="O20" t="n">
+        <v>44.63850743707478</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.007637959964458707</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.1190238966372306</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.1818561896299691</v>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>Average Burnrate (using points above average) (in/s)</t>
         </is>
       </c>
-      <c r="T16" t="n">
+      <c r="T20" t="n">
         <v>0.2197574773549804</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="C17" t="n">
-        <v>384.07962</v>
-      </c>
-      <c r="D17" t="n">
-        <v>106.12587</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2.6481368007912</v>
-      </c>
-      <c r="G17" t="n">
-        <v>472.0712174514001</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.02885696622747926</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0001749012439469829</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.0024654220005572</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.265883998706896</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="M17" t="n">
-        <v>384.080465313154</v>
-      </c>
-      <c r="N17" t="n">
-        <v>106.1258583240318</v>
-      </c>
-      <c r="O17" t="n">
-        <v>44.72838710918816</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.006885879464317112</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.09706391070413702</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.1679482796174904</v>
-      </c>
-      <c r="S17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.8200000000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>430.76083</v>
+      </c>
+      <c r="D21" t="n">
+        <v>115.01244</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8200000000000002</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.9699925402508</v>
+      </c>
+      <c r="G21" t="n">
+        <v>511.6006358568</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.02876419209701342</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0001937850440956939</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.003216990386150466</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.726464490138871</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8200000000000002</v>
+      </c>
+      <c r="M21" t="n">
+        <v>430.7610058548351</v>
+      </c>
+      <c r="N21" t="n">
+        <v>115.0124273463314</v>
+      </c>
+      <c r="O21" t="n">
+        <v>44.58458691936629</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.007629336564551877</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.1266532332017825</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.1860813796232164</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>ISP (sec)</t>
         </is>
       </c>
-      <c r="T17" t="n">
+      <c r="T21" t="n">
         <v>189.6902314107875</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.6960000000000001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>396.02133</v>
-      </c>
-      <c r="D18" t="n">
-        <v>108.09751</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.6960000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.7304720252308</v>
-      </c>
-      <c r="G18" t="n">
-        <v>480.8415059322</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02884510906582893</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0.0001797702970001744</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.002645192297557374</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.384641390248153</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.6960000000000001</v>
-      </c>
-      <c r="M18" t="n">
-        <v>396.0222015954247</v>
-      </c>
-      <c r="N18" t="n">
-        <v>108.0974981071119</v>
-      </c>
-      <c r="O18" t="n">
-        <v>44.71000847187294</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.007077574569926568</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0.1041414852740636</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0.1726237699982088</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.7370000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>406.60602</v>
-      </c>
-      <c r="D19" t="n">
-        <v>110.81244</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.7370000000000001</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2.8034509224552</v>
-      </c>
-      <c r="G19" t="n">
-        <v>492.9181118568</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.02882624292636143</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.0001840089661623492</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.002829201263719724</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.488023564935343</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.7370000000000001</v>
-      </c>
-      <c r="M19" t="n">
-        <v>406.6069148910573</v>
-      </c>
-      <c r="N19" t="n">
-        <v>110.8124278084154</v>
-      </c>
-      <c r="O19" t="n">
-        <v>44.68076589721328</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.007244451398708306</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0.1113859366727719</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0.176693936553861</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.7790000000000001</v>
-      </c>
-      <c r="C20" t="n">
-        <v>419.76904</v>
-      </c>
-      <c r="D20" t="n">
-        <v>112.45473</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.7790000000000001</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.8942067862304</v>
-      </c>
-      <c r="G20" t="n">
-        <v>500.2233790806</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.02879897945821836</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.0001940040783350489</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.003023205342054772</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.619144722263064</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0.7790000000000001</v>
-      </c>
-      <c r="M20" t="n">
-        <v>419.7699638612848</v>
-      </c>
-      <c r="N20" t="n">
-        <v>112.4547176277306</v>
-      </c>
-      <c r="O20" t="n">
-        <v>44.63850743707478</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.007637959964458707</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.1190238966372306</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.1818561896299691</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.8200000000000002</v>
-      </c>
-      <c r="C21" t="n">
-        <v>430.76083</v>
-      </c>
-      <c r="D21" t="n">
-        <v>115.01244</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.8200000000000002</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2.9699925402508</v>
-      </c>
-      <c r="G21" t="n">
-        <v>511.6006358568</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02876419209701342</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.0001937850440956939</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.003216990386150466</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.726464490138871</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.8200000000000002</v>
-      </c>
-      <c r="M21" t="n">
-        <v>430.7617780528956</v>
-      </c>
-      <c r="N21" t="n">
-        <v>115.0124273463314</v>
-      </c>
-      <c r="O21" t="n">
-        <v>44.58458691936629</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.007629336564551877</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.1266532332017825</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.1860813796232164</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -10719,7 +10791,7 @@
         <v>0.8610000000000002</v>
       </c>
       <c r="M22" t="n">
-        <v>441.7536622446603</v>
+        <v>441.7528703421784</v>
       </c>
       <c r="N22" t="n">
         <v>116.4348071898411</v>
@@ -10777,7 +10849,7 @@
         <v>0.9020000000000002</v>
       </c>
       <c r="M23" t="n">
-        <v>450.5742316576325</v>
+        <v>450.573423943101</v>
       </c>
       <c r="N23" t="n">
         <v>118.6477469463734</v>
@@ -10835,7 +10907,7 @@
         <v>0.9610000000000003</v>
       </c>
       <c r="M24" t="n">
-        <v>464.9585733157727</v>
+        <v>464.9577398153862</v>
       </c>
       <c r="N24" t="n">
         <v>120.634816727756</v>
@@ -10893,7 +10965,7 @@
         <v>1.002</v>
       </c>
       <c r="M25" t="n">
-        <v>473.6435024302174</v>
+        <v>473.6426533609347</v>
       </c>
       <c r="N25" t="n">
         <v>121.7955066000569</v>
@@ -10951,7 +11023,7 @@
         <v>1.043</v>
       </c>
       <c r="M26" t="n">
-        <v>484.3639160245093</v>
+        <v>484.3630477374524</v>
       </c>
       <c r="N26" t="n">
         <v>123.5974964018019</v>
@@ -11009,7 +11081,7 @@
         <v>1.086</v>
       </c>
       <c r="M27" t="n">
-        <v>492.5060239442723</v>
+        <v>492.5051410613987</v>
       </c>
       <c r="N27" t="n">
         <v>125.3173962125786</v>
@@ -11067,7 +11139,7 @@
         <v>1.127</v>
       </c>
       <c r="M28" t="n">
-        <v>500.5123915652879</v>
+        <v>500.5114943299303</v>
       </c>
       <c r="N28" t="n">
         <v>126.0805861286124</v>
@@ -11125,7 +11197,7 @@
         <v>1.168</v>
       </c>
       <c r="M29" t="n">
-        <v>509.7401318743924</v>
+        <v>509.7392180970769</v>
       </c>
       <c r="N29" t="n">
         <v>127.6427659567414</v>
@@ -11183,7 +11255,7 @@
         <v>1.21</v>
       </c>
       <c r="M30" t="n">
-        <v>518.0179200927709</v>
+        <v>518.0169914764136</v>
       </c>
       <c r="N30" t="n">
         <v>128.9248658156847</v>
@@ -11241,7 +11313,7 @@
         <v>1.251</v>
       </c>
       <c r="M31" t="n">
-        <v>523.5816623378729</v>
+        <v>523.5807237477641</v>
       </c>
       <c r="N31" t="n">
         <v>130.2353056715101</v>
@@ -11299,7 +11371,7 @@
         <v>1.292</v>
       </c>
       <c r="M32" t="n">
-        <v>532.5379720495924</v>
+        <v>532.5370174041013</v>
       </c>
       <c r="N32" t="n">
         <v>131.1104255752294</v>
@@ -11357,7 +11429,7 @@
         <v>1.333</v>
       </c>
       <c r="M33" t="n">
-        <v>536.7447113081002</v>
+        <v>536.7437491214669</v>
       </c>
       <c r="N33" t="n">
         <v>132.4029654330241</v>
@@ -11415,7 +11487,7 @@
         <v>1.392</v>
       </c>
       <c r="M34" t="n">
-        <v>545.8367113184572</v>
+        <v>545.8357328331987</v>
       </c>
       <c r="N34" t="n">
         <v>132.5716254144682</v>
@@ -11473,7 +11545,7 @@
         <v>1.433</v>
       </c>
       <c r="M35" t="n">
-        <v>553.1646074462419</v>
+        <v>553.1636158247501</v>
       </c>
       <c r="N35" t="n">
         <v>133.8462552742334</v>
@@ -11531,7 +11603,7 @@
         <v>1.474</v>
       </c>
       <c r="M36" t="n">
-        <v>561.7138262620051</v>
+        <v>561.7128193148959</v>
       </c>
       <c r="N36" t="n">
         <v>134.6248651885707</v>
@@ -11589,7 +11661,7 @@
         <v>1.514999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>566.7347673124696</v>
+        <v>566.7337513646524</v>
       </c>
       <c r="N37" t="n">
         <v>136.4557049871417</v>
@@ -11647,7 +11719,7 @@
         <v>1.555999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>570.2629750776143</v>
+        <v>570.2619528050132</v>
       </c>
       <c r="N38" t="n">
         <v>136.830824945871</v>
@@ -11705,7 +11777,7 @@
         <v>1.596999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>575.4196664268483</v>
+        <v>575.4186349101888</v>
       </c>
       <c r="N39" t="n">
         <v>137.1392849119342</v>
@@ -11763,7 +11835,7 @@
         <v>1.639999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>579.2192947893559</v>
+        <v>579.2182564613547</v>
       </c>
       <c r="N40" t="n">
         <v>137.5572048659546</v>
@@ -11821,7 +11893,7 @@
         <v>1.680999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>581.526239866654</v>
+        <v>581.5251974031453</v>
       </c>
       <c r="N41" t="n">
         <v>137.4109348820473</v>
@@ -11879,7 +11951,7 @@
         <v>1.723999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>584.5116664372052</v>
+        <v>584.5106186219206</v>
       </c>
       <c r="N42" t="n">
         <v>137.3412748897113</v>
@@ -11937,7 +12009,7 @@
         <v>1.764999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>586.1400800211401</v>
+        <v>586.1390292867063</v>
       </c>
       <c r="N43" t="n">
         <v>137.4288348800779</v>
@@ -11995,7 +12067,7 @@
         <v>1.823999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>588.718395695691</v>
+        <v>588.7173403392819</v>
       </c>
       <c r="N44" t="n">
         <v>137.0572049209647</v>
@@ -12053,7 +12125,7 @@
         <v>1.864999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>587.7685036050972</v>
+        <v>587.7674499514965</v>
       </c>
       <c r="N45" t="n">
         <v>136.8895449394106</v>
@@ -12111,7 +12183,7 @@
         <v>1.905999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>581.3905595680386</v>
+        <v>581.389517347755</v>
       </c>
       <c r="N46" t="n">
         <v>136.0059550366232</v>
@@ -12169,7 +12241,7 @@
         <v>1.946999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>552.2146553555159</v>
+        <v>552.2136654369401</v>
       </c>
       <c r="N47" t="n">
         <v>134.5860551928406</v>
@@ -12227,7 +12299,7 @@
         <v>1.987999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>495.7628411121204</v>
+        <v>495.7619523909668</v>
       </c>
       <c r="N48" t="n">
         <v>126.9482460331524</v>
@@ -12285,7 +12357,7 @@
         <v>2.028999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>444.3319379191233</v>
+        <v>444.3311413947376</v>
       </c>
       <c r="N49" t="n">
         <v>115.6726272736962</v>
@@ -12343,7 +12415,7 @@
         <v>2.069999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>414.0705213175233</v>
+        <v>414.0697790407714</v>
       </c>
       <c r="N50" t="n">
         <v>101.5164088311635</v>
@@ -12401,7 +12473,7 @@
         <v>2.110999999999998</v>
       </c>
       <c r="M51" t="n">
-        <v>397.7863054779972</v>
+        <v>397.7855923928787</v>
       </c>
       <c r="N51" t="n">
         <v>93.4029747238036</v>
@@ -12459,7 +12531,7 @@
         <v>2.151999999999998</v>
       </c>
       <c r="M52" t="n">
-        <v>387.3372824810021</v>
+        <v>387.3365881271538</v>
       </c>
       <c r="N52" t="n">
         <v>90.12436408451639</v>
@@ -12517,7 +12589,7 @@
         <v>2.191999999999998</v>
       </c>
       <c r="M53" t="n">
-        <v>380.5522275479433</v>
+        <v>380.5515453572129</v>
       </c>
       <c r="N53" t="n">
         <v>87.38257438616812</v>
@@ -12575,7 +12647,7 @@
         <v>2.250999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>373.5005520280858</v>
+        <v>373.4998824784262</v>
       </c>
       <c r="N54" t="n">
         <v>85.51242659192179</v>
@@ -12633,7 +12705,7 @@
         <v>2.291999999999998</v>
       </c>
       <c r="M55" t="n">
-        <v>368.2033903696943</v>
+        <v>368.202730315905</v>
       </c>
       <c r="N55" t="n">
         <v>84.68705568272912</v>
@@ -12691,7 +12763,7 @@
         <v>2.332999999999998</v>
       </c>
       <c r="M56" t="n">
-        <v>363.0467290205264</v>
+        <v>363.0460782107418</v>
       </c>
       <c r="N56" t="n">
         <v>83.24576384130006</v>
@@ -12749,7 +12821,7 @@
         <v>2.375999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>355.9902234900387</v>
+        <v>355.9895853299834</v>
       </c>
       <c r="N57" t="n">
         <v>81.83929299604</v>
@@ -12807,7 +12879,7 @@
         <v>2.416999999999998</v>
       </c>
       <c r="M58" t="n">
-        <v>346.8982234796818</v>
+        <v>346.8976016182517</v>
       </c>
       <c r="N58" t="n">
         <v>80.64725412718812</v>
@@ -12865,7 +12937,7 @@
         <v>2.457999999999998</v>
       </c>
       <c r="M59" t="n">
-        <v>337.1277219760278</v>
+        <v>337.1271176295274</v>
       </c>
       <c r="N59" t="n">
         <v>78.34227638078181</v>
@@ -12923,7 +12995,7 @@
         <v>2.498999999999998</v>
       </c>
       <c r="M60" t="n">
-        <v>321.6577479285463</v>
+        <v>321.657171314042</v>
       </c>
       <c r="N60" t="n">
         <v>76.44526558949094</v>
@@ -12981,7 +13053,7 @@
         <v>2.539999999999998</v>
       </c>
       <c r="M61" t="n">
-        <v>298.9955880519616</v>
+        <v>298.9950520624079</v>
       </c>
       <c r="N61" t="n">
         <v>72.37461803734367</v>
@@ -13039,7 +13111,7 @@
         <v>2.580999999999998</v>
       </c>
       <c r="M62" t="n">
-        <v>267.3771484637234</v>
+        <v>267.3766691544486</v>
       </c>
       <c r="N62" t="n">
         <v>67.87860153199543</v>
@@ -13097,7 +13169,7 @@
         <v>2.621999999999998</v>
       </c>
       <c r="M63" t="n">
-        <v>228.8378936436349</v>
+        <v>228.8374834211253</v>
       </c>
       <c r="N63" t="n">
         <v>59.85720541450954</v>
@@ -13155,7 +13227,7 @@
         <v>2.681999999999998</v>
       </c>
       <c r="M64" t="n">
-        <v>169.4647729708087</v>
+        <v>169.4644691825534</v>
       </c>
       <c r="N64" t="n">
         <v>47.03531882517366</v>
@@ -13213,7 +13285,7 @@
         <v>2.722999999999998</v>
       </c>
       <c r="M65" t="n">
-        <v>126.7903290496852</v>
+        <v>126.7901017610743</v>
       </c>
       <c r="N65" t="n">
         <v>39.00845270828956</v>
@@ -13271,7 +13343,7 @@
         <v>2.762999999999998</v>
       </c>
       <c r="M66" t="n">
-        <v>86.62266564567278</v>
+        <v>86.62251036296709</v>
       </c>
       <c r="N66" t="n">
         <v>28.34626688134338</v>
@@ -13329,7 +13401,7 @@
         <v>2.802999999999998</v>
       </c>
       <c r="M67" t="n">
-        <v>53.78289036942724</v>
+        <v>53.78279395640792</v>
       </c>
       <c r="N67" t="n">
         <v>18.54576895959427</v>
@@ -13387,7 +13459,7 @@
         <v>2.845999999999998</v>
       </c>
       <c r="M68" t="n">
-        <v>27.18538583164029</v>
+        <v>27.18533709820273</v>
       </c>
       <c r="N68" t="n">
         <v>12.62338261117529</v>
@@ -13445,7 +13517,7 @@
         <v>2.886999999999998</v>
       </c>
       <c r="M69" t="n">
-        <v>9.137077409566672</v>
+        <v>9.137061030134204</v>
       </c>
       <c r="N69" t="n">
         <v>7.119899916668524</v>
@@ -13503,7 +13575,7 @@
         <v>2.927999999999998</v>
       </c>
       <c r="M70" t="n">
-        <v>0.04507349920114459</v>
+        <v>0.04507341840087299</v>
       </c>
       <c r="N70" t="n">
         <v>4.238805333646586</v>
@@ -13561,7 +13633,7 @@
         <v>2.968999999999998</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.633434374109977</v>
+        <v>-0.6334332385942002</v>
       </c>
       <c r="N71" t="n">
         <v>1.984079381711563</v>
